--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11356</v>
+        <v>11378</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1849</v>
+        <v>1881</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2408</v>
+        <v>2416</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>970</v>
+        <v>987</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1285</v>
+        <v>1306</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1017</v>
+        <v>1046</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1518,11 +1518,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2069,26 +2069,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -2115,30 +2115,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>248</v>
+        <v>39</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -2161,41 +2161,87 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024.03.23 20:00-03.23 22:00</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>319</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2276,7 +2322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,7 +2400,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11356</v>
+        <v>11378</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2400,7 +2446,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1849</v>
+        <v>1881</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2446,7 +2492,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2492,7 +2538,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2538,7 +2584,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2584,7 +2630,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2408</v>
+        <v>2416</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2630,7 +2676,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2676,7 +2722,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>970</v>
+        <v>987</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2722,7 +2768,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2768,7 +2814,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2814,7 +2860,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2860,7 +2906,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2906,7 +2952,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2952,7 +2998,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1285</v>
+        <v>1306</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3044,7 +3090,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3090,7 +3136,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3136,7 +3182,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3182,7 +3228,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3228,7 +3274,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3274,7 +3320,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3320,7 +3366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1017</v>
+        <v>1046</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3366,7 +3412,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3412,7 +3458,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3458,7 +3504,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3504,7 +3550,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3582,7 +3628,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3596,11 +3642,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -3642,7 +3688,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3669,30 +3715,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>653</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -3700,12 +3746,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3720,25 +3766,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>151</v>
+        <v>659</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -3746,12 +3792,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,30 +3807,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -3792,12 +3838,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3807,30 +3853,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -3838,12 +3884,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3858,25 +3904,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>248</v>
+        <v>99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -3884,12 +3930,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3899,30 +3945,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -3930,12 +3976,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,41 +3991,87 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>315</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F38" t="n">
         <v>4</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,11 +506,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11378</v>
+        <v>11395</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1881</v>
+        <v>1912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2416</v>
+        <v>2420</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -855,22 +855,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.29 10:00-01.29 17:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -886,12 +886,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -901,30 +901,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.30 10:00-01.30 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>481</v>
+        <v>1321</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -932,12 +932,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -947,30 +947,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>438</v>
+        <v>661</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -978,12 +978,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -993,43 +993,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1306</v>
+        <v>105</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>640</v>
+        <v>7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -1085,43 +1085,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>972</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -1131,30 +1131,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>960</v>
+        <v>518</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1192,15 +1192,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>492</v>
+        <v>666</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,21 +1228,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>643</v>
+        <v>1079</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1250,16 +1250,16 @@
         </is>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,43 +1269,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1046</v>
+        <v>204</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,26 +1315,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>200</v>
+        <v>927</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -1361,30 +1361,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>918</v>
+        <v>131</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>123</v>
+        <v>269</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1453,30 +1453,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>252</v>
+        <v>113</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1499,30 +1499,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>113</v>
+        <v>259</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1545,26 +1545,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>253</v>
+        <v>463</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,30 +1591,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>659</v>
+        <v>491</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1642,25 +1642,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>160</v>
+        <v>668</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1729,41 +1729,87 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>104</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>315</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="n">
+        <v>320</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1780,7 +1826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,7 +1904,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1904,7 +1950,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1950,7 +1996,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1996,7 +2042,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2069,43 +2115,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -2115,26 +2161,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2146,12 +2192,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -2161,30 +2207,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>319</v>
+        <v>42</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -2192,12 +2238,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -2207,41 +2253,87 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.03.23 20:00-03.23 22:00</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>360</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2258,7 +2350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,6 +2400,52 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>天河路299号B1层 天河时尚街</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024.02.01 00:00-03.01 23:59</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2400,11 +2538,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11378</v>
+        <v>11395</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2446,7 +2584,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1881</v>
+        <v>1912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2492,7 +2630,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2538,7 +2676,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2584,7 +2722,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2630,7 +2768,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2416</v>
+        <v>2420</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2676,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2722,7 +2860,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2768,7 +2906,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2814,7 +2952,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2841,22 +2979,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.29 10:00-01.29 17:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2864,7 +3002,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -2872,12 +3010,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -2887,30 +3025,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>天河路299号B1层 天河时尚街</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.30 10:00-01.30 17:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>481</v>
+        <v>23</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -2918,12 +3056,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -2933,30 +3071,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>438</v>
+        <v>1321</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -2964,12 +3102,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -2984,38 +3122,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1306</v>
+        <v>5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -3030,38 +3168,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>661</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -3071,43 +3209,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>640</v>
+        <v>105</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -3122,25 +3260,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>86</v>
+        <v>879</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -3148,12 +3286,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -3163,43 +3301,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>864</v>
+        <v>7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3366,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3274,7 +3412,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3320,7 +3458,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>643</v>
+        <v>666</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3366,7 +3504,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1046</v>
+        <v>1079</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3412,7 +3550,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3458,7 +3596,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3504,7 +3642,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3550,7 +3688,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3688,7 +3826,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3715,43 +3853,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,30 +3899,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>659</v>
+        <v>3</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -3792,12 +3930,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3807,26 +3945,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>160</v>
+        <v>463</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3838,12 +3976,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3853,30 +3991,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>39</v>
+        <v>491</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -3884,12 +4022,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3899,30 +4037,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>99</v>
+        <v>668</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -3930,12 +4068,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,30 +4083,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -3976,12 +4114,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,30 +4129,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>315</v>
+        <v>42</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -4022,12 +4160,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -4037,41 +4175,179 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>104</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.03.23 20:00-03.23 22:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>360</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>320</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F41" t="n">
         <v>4</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11395</v>
+        <v>11421</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1912</v>
+        <v>1944</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2420</v>
+        <v>2426</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1079</v>
+        <v>1128</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>269</v>
+        <v>138</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1453,30 +1453,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>113</v>
+        <v>308</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,30 +1499,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>259</v>
+        <v>113</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1545,26 +1545,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>463</v>
+        <v>266</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1637,30 +1637,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>668</v>
+        <v>506</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1688,25 +1688,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>172</v>
+        <v>683</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1729,26 +1729,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1775,41 +1775,87 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>113</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>320</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F31" t="n">
+        <v>327</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1904,7 +1950,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1950,7 +1996,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1996,7 +2042,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2042,7 +2088,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>879</v>
+        <v>898</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2134,7 +2180,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2166,7 +2212,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2180,7 +2226,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2226,7 +2272,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2272,7 +2318,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2428,7 +2474,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2460,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2538,7 +2584,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11395</v>
+        <v>11421</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2584,7 +2630,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1912</v>
+        <v>1944</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2630,7 +2676,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2676,7 +2722,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2722,7 +2768,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2768,7 +2814,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2420</v>
+        <v>2426</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2814,7 +2860,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2860,7 +2906,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2906,7 +2952,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2952,7 +2998,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2998,7 +3044,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3044,7 +3090,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3090,7 +3136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3136,7 +3182,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3182,7 +3228,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3228,7 +3274,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3274,7 +3320,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>879</v>
+        <v>898</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3311,7 +3357,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3320,7 +3366,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3357,7 +3403,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3366,7 +3412,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3412,7 +3458,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3458,7 +3504,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3504,7 +3550,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1079</v>
+        <v>1128</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3550,7 +3596,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3596,7 +3642,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3628,21 +3674,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3654,12 +3700,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -3674,25 +3720,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>269</v>
+        <v>138</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -3700,12 +3746,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3720,25 +3766,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -3746,12 +3792,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,30 +3807,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -3792,12 +3838,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3807,30 +3853,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>259</v>
+        <v>113</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -3838,12 +3884,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3853,43 +3899,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>266</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3899,43 +3945,43 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>【大会员抢先购】广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,25 +3996,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>463</v>
+        <v>100</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -3976,12 +4022,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,30 +4037,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>491</v>
+        <v>100</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -4022,12 +4068,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -4037,30 +4083,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>668</v>
+        <v>471</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -4068,12 +4114,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -4083,26 +4129,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>172</v>
+        <v>506</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4114,12 +4160,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -4129,30 +4175,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>42</v>
+        <v>683</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -4160,12 +4206,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4175,26 +4221,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4206,12 +4252,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -4221,30 +4267,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>360</v>
+        <v>43</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -4252,12 +4298,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -4267,30 +4313,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>320</v>
+        <v>113</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -4298,12 +4344,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -4313,41 +4359,133 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.03.23 20:00-03.23 22:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>392</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>327</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F43" t="n">
         <v>4</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -506,22 +501,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11421</v>
+        <v>11498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已停售</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80066</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80066</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/A6Y7rq9y1703560330806.jpeg</t>
         </is>
@@ -538,38 +530,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州.星火.AI次元动漫展</t>
+          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>沙滘中路41-50号 火星工厂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.01.27 12:00-01.29 00:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1944</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>782</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78754</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Yq9dmngw1704858430914.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
         </is>
       </c>
     </row>
@@ -579,43 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·妖都魔法少女小圆ONLY</t>
+          <t>广州·文豪野犬only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄内国际会议厅 颐和山庄</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.01.28 10:00-01.28 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>530</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>626</v>
+      </c>
+      <c r="G4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80436</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79748</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/usRmAiWv1702894629137.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ghqTgq3H1705290829994.jpeg</t>
         </is>
       </c>
     </row>
@@ -625,43 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·第七届萌物语动漫嘉年华</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>850</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>484</v>
+      </c>
+      <c r="G5" t="n">
+        <v>68</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79317</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/YY2vfMJS1705657564136.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -671,43 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·第五人格only唐人街春市</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:30</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2426</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
+        <v>1430</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79038</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/VUDfqbd61701069000614.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -717,43 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>沙滘中路41-50号 火星工厂</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.29 00:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>768</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
+        <v>726</v>
+      </c>
+      <c r="G7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -763,43 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·蓝锁only2.0</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大石街石北工业大道644号 巨大创意产业园</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79750</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/ERj7a4FV1702459336221.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -809,43 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·文豪野犬only</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>599</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>63</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80436</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ghqTgq3H1705290829994.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,43 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>459</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>1040</v>
+      </c>
+      <c r="G10" t="n">
+        <v>63</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,43 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1349</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -947,43 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>680</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>713</v>
+      </c>
+      <c r="G12" t="n">
+        <v>58</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -993,12 +935,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1008,28 +950,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
+        <v>1209</v>
+      </c>
+      <c r="G13" t="n">
+        <v>58</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -1039,43 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -1085,43 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>992</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>972</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -1131,43 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>542</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -1177,43 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>678</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1223,43 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1128</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,43 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>214</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>349</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,43 +1222,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>938</v>
+        <v>113</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1361,43 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>274</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1407,43 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>138</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>498</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1453,43 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>308</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>522</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,43 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>113</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>710</v>
+      </c>
+      <c r="G24" t="n">
+        <v>39</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1545,43 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>266</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,43 +1470,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>471</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1637,225 +1511,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>506</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>344</v>
+      </c>
+      <c r="G27" t="n">
+        <v>69</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>广州·代号鸢only2.0</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>清河东路288号 科尔海悦酒店</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>683</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>179</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>广州·排球少年ONLY</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>113</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>327</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1872,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1911,15 +1596,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1931,43 +1611,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·七音阿卡莉 NANAOAKARI 2024 专场演出</t>
+          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 20:00-01.27 22:00</t>
+          <t>2024.01.28 19:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79638</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/YLZDdSYM1703644823436.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
         </is>
       </c>
     </row>
@@ -1977,43 +1652,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.28 19:00-01.28 21:00</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -2023,43 +1693,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
+        <v>934</v>
+      </c>
+      <c r="G4" t="n">
+        <v>380</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -2069,43 +1734,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>898</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>420</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2115,43 +1775,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="G6" t="n">
+        <v>288</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -2180,22 +1835,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>78</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
@@ -2226,22 +1876,17 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="G8" t="n">
+        <v>380</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
@@ -2272,22 +1917,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>380</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
@@ -2318,22 +1958,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>392</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>463</v>
+      </c>
+      <c r="G10" t="n">
+        <v>480</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
@@ -2345,41 +1980,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>280</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2396,7 +2067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2435,15 +2106,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2474,22 +2140,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
@@ -2506,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,15 +2206,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2584,22 +2240,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11421</v>
+        <v>11498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已停售</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80066</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80066</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/A6Y7rq9y1703560330806.jpeg</t>
         </is>
@@ -2616,38 +2269,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州.星火.AI次元动漫展</t>
+          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>沙滘中路41-50号 火星工厂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.01.27 12:00-01.29 00:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1944</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>782</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78754</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Yq9dmngw1704858430914.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
         </is>
       </c>
     </row>
@@ -2657,43 +2305,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·七音阿卡莉 NANAOAKARI 2024 专场演出</t>
+          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.27 20:00-01.27 22:00</t>
+          <t>2024.01.28 19:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79638</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/YLZDdSYM1703644823436.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
         </is>
       </c>
     </row>
@@ -2703,43 +2346,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·妖都魔法少女小圆ONLY</t>
+          <t>广州·文豪野犬only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄内国际会议厅 颐和山庄</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.01.28 10:00-01.28 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>530</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>626</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80436</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79748</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/usRmAiWv1702894629137.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ghqTgq3H1705290829994.jpeg</t>
         </is>
       </c>
     </row>
@@ -2749,43 +2387,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·第七届萌物语动漫嘉年华</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>850</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
+        <v>484</v>
+      </c>
+      <c r="G6" t="n">
+        <v>68</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79317</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/YY2vfMJS1705657564136.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -2795,43 +2428,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·第五人格only唐人街春市</t>
+          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>天河路299号B1层 天河时尚街</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:30</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2426</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79038</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/VUDfqbd61701069000614.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -2841,43 +2469,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>沙滘中路41-50号 火星工厂</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.29 00:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>768</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
+        <v>1430</v>
+      </c>
+      <c r="G8" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -2887,43 +2510,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·蓝锁only2.0</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>大石街石北工业大道644号 巨大创意产业园</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79750</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/ERj7a4FV1702459336221.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -2933,43 +2551,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.28 19:00-01.28 21:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>726</v>
+      </c>
+      <c r="G10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2592,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·文豪野犬only</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2994,28 +2607,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>599</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80436</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ghqTgq3H1705290829994.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -3025,43 +2633,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>459</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>934</v>
+      </c>
+      <c r="G12" t="n">
+        <v>380</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -3071,43 +2674,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>天河路299号B1层 天河时尚街</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>63</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -3117,43 +2715,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1349</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>1040</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -3163,43 +2756,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
+        <v>600</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -3209,43 +2797,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>680</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>713</v>
+      </c>
+      <c r="G16" t="n">
+        <v>58</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -3255,12 +2838,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3270,28 +2853,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>122</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
+        <v>1209</v>
+      </c>
+      <c r="G17" t="n">
+        <v>58</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -3301,43 +2879,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>898</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
+        <v>240</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -3347,43 +2920,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>972</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -3393,43 +2961,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>992</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -3439,43 +3002,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>542</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3485,43 +3043,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>678</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G22" t="n">
+        <v>55</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -3531,43 +3084,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1128</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
+        <v>349</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3577,43 +3125,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>214</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>420</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,43 +3166,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>938</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="G25" t="n">
+        <v>288</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3669,43 +3207,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3715,43 +3250,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>138</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>274</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,43 +3291,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>308</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>78</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3807,43 +3332,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="G29" t="n">
+        <v>380</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3853,43 +3373,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>113</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="G30" t="n">
+        <v>380</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3899,43 +3414,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>266</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
+        <v>498</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,43 +3455,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>1</v>
+        <v>522</v>
+      </c>
+      <c r="G32" t="n">
+        <v>60</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,43 +3496,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
+        <v>710</v>
+      </c>
+      <c r="G33" t="n">
+        <v>39</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4037,43 +3537,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="G34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -4083,43 +3578,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>471</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="G35" t="n">
+        <v>380</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -4129,43 +3619,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>506</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="G36" t="n">
+        <v>60</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -4175,43 +3660,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>683</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
+        <v>463</v>
+      </c>
+      <c r="G37" t="n">
+        <v>480</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -4221,43 +3701,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>179</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>64</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -4267,43 +3742,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
+        <v>344</v>
+      </c>
+      <c r="G39" t="n">
+        <v>69</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -4313,179 +3783,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>113</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>280</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>392</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>327</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·《FGO》FES2024·广州特别纪念展</t>
+          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新港东路1000号 保利世贸博览馆</t>
+          <t>沙滘中路41-50号 火星工厂</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.26 09:00-01.28 17:00</t>
+          <t>2024.01.27 12:00-01.29 00:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11498</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80066</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/A6Y7rq9y1703560330806.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,38 +523,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>沙滘中路41-50号 火星工厂</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.29 00:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>782</v>
-      </c>
-      <c r="G3" t="n">
-        <v>48</v>
+        <v>490</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -566,38 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·文豪野犬only</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>626</v>
+        <v>1462</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80436</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ghqTgq3H1705290829994.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>484</v>
+        <v>748</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1430</v>
+        <v>170</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>726</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>157</v>
+        <v>1057</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>628</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1040</v>
+        <v>727</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>600</v>
+        <v>1256</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>713</v>
+        <v>252</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1209</v>
+        <v>983</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>972</v>
+        <v>171</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>161</v>
+        <v>367</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
-      </c>
-      <c r="G18" t="n">
-        <v>55</v>
+        <v>113</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1183,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,40 +1224,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>113</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>509</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,38 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>274</v>
+        <v>530</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>498</v>
+        <v>718</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>522</v>
+        <v>206</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>710</v>
+        <v>143</v>
       </c>
       <c r="G24" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,118 +1429,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>197</v>
+        <v>349</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>广州·排球少年ONLY</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>133</v>
-      </c>
-      <c r="G26" t="n">
-        <v>60</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>344</v>
-      </c>
-      <c r="G27" t="n">
-        <v>69</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1632,8 +1550,10 @@
       <c r="F2" t="n">
         <v>39</v>
       </c>
-      <c r="G2" t="n">
-        <v>100</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1712,7 +1632,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>934</v>
+        <v>950</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -1794,7 +1714,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="G6" t="n">
         <v>288</v>
@@ -1835,7 +1755,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>78</v>
@@ -1876,7 +1796,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1917,7 +1837,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -1958,10 +1878,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>463</v>
+        <v>552</v>
       </c>
       <c r="G10" t="n">
-        <v>480</v>
+        <v>580</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1999,7 +1919,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>64</v>
@@ -2140,7 +2060,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2167,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,40 +2141,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·《FGO》FES2024·广州特别纪念展</t>
+          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新港东路1000号 保利世贸博览馆</t>
+          <t>沙滘中路41-50号 火星工厂</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.26 09:00-01.28 17:00</t>
+          <t>2024.01.27 12:00-01.29 00:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11498</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80066</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/A6Y7rq9y1703560330806.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
         </is>
       </c>
     </row>
@@ -2264,38 +2182,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
+          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>沙滘中路41-50号 火星工厂</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.29 00:00</t>
+          <t>2024.01.28 19:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>782</v>
-      </c>
-      <c r="G3" t="n">
-        <v>48</v>
+        <v>39</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
         </is>
       </c>
     </row>
@@ -2305,38 +2225,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 19:00-01.28 21:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
-      </c>
-      <c r="G4" t="n">
-        <v>100</v>
+        <v>490</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -2346,38 +2268,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·文豪野犬only</t>
+          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>天河路299号B1层 天河时尚街</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>626</v>
+        <v>154</v>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80436</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ghqTgq3H1705290829994.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -2387,38 +2309,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>484</v>
+        <v>1462</v>
       </c>
       <c r="G6" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -2428,38 +2350,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>天河路299号B1层 天河时尚街</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -2474,33 +2396,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1430</v>
+        <v>748</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -2510,38 +2432,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -2551,38 +2473,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>726</v>
+        <v>950</v>
       </c>
       <c r="G10" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -2592,38 +2514,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -2633,38 +2555,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>934</v>
+        <v>1057</v>
       </c>
       <c r="G12" t="n">
-        <v>380</v>
+        <v>63</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -2674,38 +2596,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>628</v>
       </c>
       <c r="G13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2715,38 +2637,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1040</v>
+        <v>727</v>
       </c>
       <c r="G14" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2756,38 +2678,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>600</v>
+        <v>1256</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2797,38 +2719,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>713</v>
+        <v>252</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2838,38 +2760,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1209</v>
+        <v>983</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2879,38 +2801,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2920,38 +2842,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>972</v>
+        <v>171</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2966,33 +2888,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -3007,33 +2929,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>161</v>
+        <v>367</v>
       </c>
       <c r="G21" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3048,33 +2970,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3084,38 +3006,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>349</v>
+        <v>180</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3047,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" t="n">
-        <v>420</v>
+        <v>113</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3090,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>151</v>
+        <v>279</v>
       </c>
       <c r="G25" t="n">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3207,40 +3131,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>113</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3250,38 +3172,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3291,38 +3213,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3337,33 +3259,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>121</v>
+        <v>509</v>
       </c>
       <c r="G29" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3373,38 +3295,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>121</v>
+        <v>530</v>
       </c>
       <c r="G30" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3414,38 +3336,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>498</v>
+        <v>718</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3455,38 +3377,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>522</v>
+        <v>206</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3496,38 +3418,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>710</v>
+        <v>55</v>
       </c>
       <c r="G33" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3537,38 +3459,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3578,38 +3500,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>53</v>
+        <v>552</v>
       </c>
       <c r="G35" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3619,38 +3541,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3660,38 +3582,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>463</v>
+        <v>349</v>
       </c>
       <c r="G37" t="n">
-        <v>480</v>
+        <v>69</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3701,118 +3623,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>344</v>
-      </c>
-      <c r="G39" t="n">
-        <v>69</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" t="n">
-        <v>280</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>沙滘中路41-50号 火星工厂</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.29 00:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>785</v>
-      </c>
-      <c r="G2" t="n">
-        <v>48</v>
+        <v>492</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -523,40 +525,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>490</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1478</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -571,33 +571,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1462</v>
+        <v>767</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>748</v>
+        <v>182</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>1069</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1057</v>
+        <v>643</v>
       </c>
       <c r="G8" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -786,23 +786,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>628</v>
+        <v>735</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>727</v>
+        <v>1282</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1256</v>
+        <v>258</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>252</v>
+        <v>993</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>983</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="G14" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>380</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>367</v>
-      </c>
-      <c r="G17" t="n">
-        <v>60</v>
+        <v>113</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1140,40 +1142,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>113</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>282</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1183,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>279</v>
+        <v>519</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1239,23 +1239,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,38 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>530</v>
+        <v>729</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>718</v>
+        <v>212</v>
       </c>
       <c r="G22" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,77 +1388,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>143</v>
+        <v>354</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>349</v>
-      </c>
-      <c r="G25" t="n">
-        <v>69</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1475,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,40 +1488,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.28 19:00-01.28 21:00</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -1572,38 +1529,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>961</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -1613,38 +1570,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -1654,38 +1611,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="G5" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1695,38 +1652,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1736,38 +1693,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -1777,38 +1734,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -1818,38 +1775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>556</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -1859,38 +1816,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>552</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>580</v>
+        <v>64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -1900,77 +1857,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="n">
-        <v>280</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2060,7 +1976,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2087,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2141,38 +2057,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·第五届ACBC动漫盛典-二次元游园会</t>
+          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>沙滘中路41-50号 火星工厂</t>
+          <t>东圃中山大道中358号 轰谧斯酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.29 00:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>785</v>
-      </c>
-      <c r="G2" t="n">
-        <v>48</v>
+        <v>492</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/QrQcGQoV1704268205303.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
         </is>
       </c>
     </row>
@@ -2182,40 +2100,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·《卡农》世界经典音乐之旅音乐会</t>
+          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>天河路299号B1层 天河时尚街</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.28 19:00-01.28 21:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>165</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80047</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oyFC3Nma1703055804290.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -2225,40 +2141,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>490</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1478</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -2268,38 +2182,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>天河路299号B1层 天河时尚街</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -2314,33 +2228,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1462</v>
+        <v>767</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -2350,38 +2264,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -2391,38 +2305,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>748</v>
+        <v>961</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -2432,38 +2346,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -2473,38 +2387,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>950</v>
+        <v>1069</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>63</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -2514,38 +2428,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>643</v>
       </c>
       <c r="G11" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2555,38 +2469,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1057</v>
+        <v>735</v>
       </c>
       <c r="G12" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2596,38 +2510,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>628</v>
+        <v>1282</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2637,38 +2551,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>727</v>
+        <v>258</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2678,38 +2592,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1256</v>
+        <v>993</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2719,38 +2633,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>252</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2760,38 +2674,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>983</v>
+        <v>173</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2806,33 +2720,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2847,33 +2761,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>171</v>
+        <v>380</v>
       </c>
       <c r="G19" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2888,33 +2802,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2924,38 +2838,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>367</v>
+        <v>205</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -2965,38 +2879,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" t="n">
-        <v>420</v>
+        <v>113</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3006,38 +2922,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>180</v>
+        <v>282</v>
       </c>
       <c r="G23" t="n">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3047,40 +2963,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>113</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3090,38 +3004,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>279</v>
+        <v>127</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3131,38 +3045,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3177,33 +3091,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>123</v>
+        <v>519</v>
       </c>
       <c r="G27" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3213,38 +3127,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>123</v>
+        <v>536</v>
       </c>
       <c r="G28" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3168,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>509</v>
+        <v>729</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3209,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>530</v>
+        <v>212</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3336,38 +3250,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>718</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3377,38 +3291,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3418,38 +3332,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>55</v>
+        <v>556</v>
       </c>
       <c r="G33" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3459,38 +3373,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3500,38 +3414,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>552</v>
+        <v>354</v>
       </c>
       <c r="G35" t="n">
-        <v>580</v>
+        <v>69</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3541,118 +3455,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>349</v>
-      </c>
-      <c r="G37" t="n">
-        <v>69</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>6</v>
-      </c>
-      <c r="G38" t="n">
-        <v>280</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1478</v>
+        <v>1504</v>
       </c>
       <c r="G3" t="n">
         <v>35</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1069</v>
+        <v>1091</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1282</v>
+        <v>1319</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>48.8</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -981,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>380</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,40 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>113</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>404</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1142,38 +1140,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>282</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1183,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>519</v>
+        <v>288</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1239,23 +1239,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,38 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>729</v>
+        <v>544</v>
       </c>
       <c r="G21" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>212</v>
+        <v>735</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,36 +1388,77 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>158</v>
+      </c>
+      <c r="G24" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>354</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F25" t="n">
+        <v>360</v>
+      </c>
+      <c r="G25" t="n">
         <v>69</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1434,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1548,7 +1589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>961</v>
+        <v>975</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1630,7 +1671,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1671,7 +1712,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1712,7 +1753,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1753,7 +1794,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1794,7 +1835,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="G9" t="n">
         <v>580</v>
@@ -1816,38 +1857,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -1857,36 +1898,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>280</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -1976,7 +2058,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2003,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2076,7 +2158,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2119,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -2160,7 +2242,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1478</v>
+        <v>1504</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2242,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -2283,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2324,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>961</v>
+        <v>975</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2365,7 +2447,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2406,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1069</v>
+        <v>1091</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -2447,7 +2529,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2488,7 +2570,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2529,7 +2611,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1282</v>
+        <v>1319</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -2570,7 +2652,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2611,7 +2693,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2633,38 +2715,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>48.8</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2679,33 +2761,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2720,33 +2802,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2761,33 +2843,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>380</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2802,33 +2884,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·砂糖桔动漫荟STJ01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="G20" t="n">
-        <v>420</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2838,38 +2920,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>205</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2884,35 +2966,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>113</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>223</v>
+      </c>
+      <c r="G22" t="n">
+        <v>288</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -2922,38 +3002,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>282</v>
-      </c>
-      <c r="G23" t="n">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -2963,38 +3045,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>288</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3004,38 +3086,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3146,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3091,33 +3173,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>519</v>
+        <v>130</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3209,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3142,23 +3224,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3168,38 +3250,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>729</v>
+        <v>544</v>
       </c>
       <c r="G29" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3214,33 +3296,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>212</v>
+        <v>735</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3250,38 +3332,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="G31" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3291,38 +3373,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3337,33 +3419,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>556</v>
+        <v>158</v>
       </c>
       <c r="G33" t="n">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3373,38 +3455,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>574</v>
       </c>
       <c r="G34" t="n">
-        <v>64</v>
+        <v>580</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3414,38 +3496,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>354</v>
+        <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>69</v>
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3455,36 +3537,159 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2024.03.31 19:00-03.31 20:30</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>38</v>
+      </c>
+      <c r="G36" t="n">
+        <v>380</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>64</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>360</v>
+      </c>
+      <c r="G38" t="n">
+        <v>69</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F39" t="n">
         <v>6</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G39" t="n">
         <v>280</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1504</v>
+        <v>1520</v>
       </c>
       <c r="G3" t="n">
         <v>35</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1319</v>
+        <v>1349</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="G22" t="n">
         <v>39</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G25" t="n">
         <v>69</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1835,10 +1835,12 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>574</v>
-      </c>
-      <c r="G9" t="n">
-        <v>580</v>
+        <v>581</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1876,7 +1878,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -1917,7 +1919,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
         <v>64</v>
@@ -2058,7 +2060,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2085,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2201,7 +2203,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -2242,7 +2244,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1504</v>
+        <v>1520</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2324,7 +2326,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -2365,7 +2367,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2406,7 +2408,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2447,7 +2449,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2488,7 +2490,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -2529,7 +2531,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2570,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2611,7 +2613,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1319</v>
+        <v>1349</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -2652,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2693,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2734,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2775,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
         <v>48.8</v>
@@ -2816,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2857,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2898,7 +2900,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -2980,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3146,7 +3148,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3173,33 +3175,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>130</v>
+        <v>530</v>
       </c>
       <c r="G27" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3211,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3224,23 +3226,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3250,38 +3252,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>544</v>
+        <v>738</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3296,33 +3298,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>735</v>
+        <v>222</v>
       </c>
       <c r="G30" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3332,38 +3334,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>218</v>
+        <v>59</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3373,38 +3375,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3419,33 +3421,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>158</v>
-      </c>
-      <c r="G33" t="n">
-        <v>60</v>
+        <v>581</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3455,38 +3459,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>574</v>
+        <v>56</v>
       </c>
       <c r="G34" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3519,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G35" t="n">
         <v>380</v>
@@ -3537,38 +3541,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3578,38 +3582,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>361</v>
       </c>
       <c r="G37" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3619,77 +3623,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>6</v>
-      </c>
-      <c r="G39" t="n">
-        <v>280</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1520</v>
+        <v>1558</v>
       </c>
       <c r="G3" t="n">
         <v>35</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1102</v>
+        <v>1118</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1349</v>
+        <v>1381</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1140,40 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1181,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>288</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1224,38 +1224,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>530</v>
+        <v>290</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1280,23 +1280,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>738</v>
+        <v>556</v>
       </c>
       <c r="G22" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,33 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>222</v>
+        <v>744</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,36 +1429,77 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>168</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>361</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F26" t="n">
+        <v>366</v>
+      </c>
+      <c r="G26" t="n">
         <v>69</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1589,7 +1630,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1671,7 +1712,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1712,7 +1753,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1753,7 +1794,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1794,7 +1835,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1835,7 +1876,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1878,7 +1919,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2060,7 +2101,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2087,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2160,7 +2201,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2203,7 +2244,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -2244,7 +2285,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1520</v>
+        <v>1558</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2326,7 +2367,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -2367,7 +2408,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2408,7 +2449,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2449,7 +2490,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2490,7 +2531,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1102</v>
+        <v>1118</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -2531,7 +2572,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2572,7 +2613,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2613,7 +2654,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1349</v>
+        <v>1381</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -2654,7 +2695,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2695,7 +2736,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2736,7 +2777,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2777,7 +2818,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
         <v>48.8</v>
@@ -2818,7 +2859,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2859,7 +2900,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2886,7 +2927,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2900,7 +2941,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -2927,33 +2968,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>420</v>
+        <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -2963,38 +3004,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,35 +3050,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>114</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>249</v>
+      </c>
+      <c r="G23" t="n">
+        <v>288</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3047,38 +3086,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>288</v>
-      </c>
-      <c r="G24" t="n">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3088,38 +3129,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>290</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3170,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3175,33 +3216,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>530</v>
+        <v>138</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3211,38 +3252,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>549</v>
+        <v>138</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3252,38 +3293,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>738</v>
+        <v>536</v>
       </c>
       <c r="G29" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3293,38 +3334,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>222</v>
+        <v>556</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3334,38 +3375,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>744</v>
       </c>
       <c r="G31" t="n">
-        <v>380</v>
+        <v>39</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3375,38 +3416,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3416,40 +3457,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>581</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="G33" t="n">
+        <v>380</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3459,38 +3498,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="G34" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3500,38 +3539,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>56</v>
-      </c>
-      <c r="G35" t="n">
-        <v>380</v>
+        <v>583</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3541,38 +3582,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="G36" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3582,38 +3623,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>361</v>
+        <v>74</v>
       </c>
       <c r="G37" t="n">
-        <v>69</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,36 +3664,118 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>12</v>
+      </c>
+      <c r="G38" t="n">
+        <v>64</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>366</v>
+      </c>
+      <c r="G39" t="n">
+        <v>69</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F40" t="n">
         <v>6</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G40" t="n">
         <v>280</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1558</v>
+        <v>1569</v>
       </c>
       <c r="G3" t="n">
         <v>35</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1381</v>
+        <v>1398</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="G23" t="n">
         <v>39</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1558</v>
+        <v>1569</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1381</v>
+        <v>1398</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
         <v>48.8</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G23" t="n">
         <v>288</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="G31" t="n">
         <v>39</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G33" t="n">
         <v>380</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1569</v>
+        <v>1582</v>
       </c>
       <c r="G3" t="n">
         <v>35</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1398</v>
+        <v>1427</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,40 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>114</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>292</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1265,38 +1263,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>545</v>
-      </c>
-      <c r="G21" t="n">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>559</v>
+        <v>294</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>751</v>
+        <v>550</v>
       </c>
       <c r="G23" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>237</v>
+        <v>564</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>171</v>
+        <v>754</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1470,36 +1470,118 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024.03.16 10:00-03.16 17:00</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>242</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>176</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>366</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F28" t="n">
+        <v>368</v>
+      </c>
+      <c r="G28" t="n">
         <v>69</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1630,7 +1712,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1712,7 +1794,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1794,7 +1876,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1876,7 +1958,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1919,7 +2001,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2101,7 +2183,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2128,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2201,7 +2283,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2244,7 +2326,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -2285,7 +2367,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1569</v>
+        <v>1582</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2367,7 +2449,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -2408,7 +2490,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2449,7 +2531,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2490,7 +2572,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2531,7 +2613,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -2572,7 +2654,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2613,7 +2695,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2654,7 +2736,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1398</v>
+        <v>1427</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -2695,7 +2777,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2736,7 +2818,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2777,7 +2859,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2818,7 +2900,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
         <v>48.8</v>
@@ -2859,7 +2941,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2900,7 +2982,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2941,7 +3023,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -2968,12 +3050,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2982,19 +3064,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,33 +3091,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>420</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3045,38 +3127,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3091,35 +3173,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>114</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>35</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3209,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3170,38 +3250,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
-      </c>
-      <c r="G26" t="n">
-        <v>78</v>
+        <v>114</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3211,38 +3293,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>140</v>
+        <v>294</v>
       </c>
       <c r="G27" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3252,38 +3334,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3298,33 +3380,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>545</v>
+        <v>143</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3334,38 +3416,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>559</v>
+        <v>143</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3375,38 +3457,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>751</v>
+        <v>550</v>
       </c>
       <c r="G31" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3416,38 +3498,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>237</v>
+        <v>564</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3457,38 +3539,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
+        <v>754</v>
       </c>
       <c r="G33" t="n">
-        <v>380</v>
+        <v>39</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3498,38 +3580,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3539,40 +3621,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>583</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="G35" t="n">
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3582,38 +3662,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="G36" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,38 +3703,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>76</v>
-      </c>
-      <c r="G37" t="n">
-        <v>380</v>
+        <v>585</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3664,38 +3746,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="G38" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3705,38 +3787,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="G39" t="n">
-        <v>69</v>
+        <v>380</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3746,36 +3828,118 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>12</v>
+      </c>
+      <c r="G40" t="n">
+        <v>64</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>368</v>
+      </c>
+      <c r="G41" t="n">
+        <v>69</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F42" t="n">
         <v>6</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G42" t="n">
         <v>280</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1582</v>
+        <v>1593</v>
       </c>
       <c r="G3" t="n">
         <v>35</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1427</v>
+        <v>1446</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="G25" t="n">
         <v>39</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G28" t="n">
         <v>69</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1958,12 +1958,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>585</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>587</v>
+      </c>
+      <c r="G9" t="n">
+        <v>580</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2001,7 +1999,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2042,7 +2040,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
         <v>64</v>
@@ -2183,7 +2181,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2283,7 +2281,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2326,7 +2324,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -2367,7 +2365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1582</v>
+        <v>1593</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2408,7 +2406,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
@@ -2449,7 +2447,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -2490,7 +2488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2531,7 +2529,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2572,7 +2570,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2613,7 +2611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -2654,7 +2652,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2695,7 +2693,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2736,7 +2734,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1427</v>
+        <v>1446</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -2777,7 +2775,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2818,7 +2816,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2859,7 +2857,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2900,7 +2898,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
         <v>48.8</v>
@@ -2941,7 +2939,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2982,7 +2980,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3023,7 +3021,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3064,7 +3062,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -3105,7 +3103,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>35</v>
@@ -3228,7 +3226,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G25" t="n">
         <v>288</v>
@@ -3312,7 +3310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3394,7 +3392,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G29" t="n">
         <v>380</v>
@@ -3435,7 +3433,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G30" t="n">
         <v>380</v>
@@ -3476,7 +3474,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3517,7 +3515,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3558,7 +3556,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="G33" t="n">
         <v>39</v>
@@ -3599,7 +3597,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3640,7 +3638,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G35" t="n">
         <v>380</v>
@@ -3681,7 +3679,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3722,12 +3720,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>585</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>587</v>
+      </c>
+      <c r="G37" t="n">
+        <v>580</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3765,7 +3761,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G38" t="n">
         <v>380</v>
@@ -3806,7 +3802,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -3847,7 +3843,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G40" t="n">
         <v>64</v>
@@ -3888,7 +3884,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G41" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>511</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1610</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -530,33 +528,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1593</v>
+        <v>847</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>841</v>
+        <v>252</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,19 +665,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>1159</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1147</v>
+        <v>768</v>
       </c>
       <c r="G7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,12 +728,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -745,23 +743,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>749</v>
+        <v>803</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>795</v>
+        <v>1476</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1446</v>
+        <v>296</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>289</v>
+        <v>1040</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -899,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1035</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G14" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1020,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1061,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>490</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1102,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>473</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1143,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1159,19 +1157,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1225,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>35</v>
+        <v>115</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1263,40 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>114</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>297</v>
+        <v>563</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1345,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1362,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1434,33 +1432,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>759</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1475,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>246</v>
+        <v>764</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1511,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1552,36 +1550,77 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>187</v>
+      </c>
+      <c r="G28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>370</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F29" t="n">
+        <v>372</v>
+      </c>
+      <c r="G29" t="n">
         <v>69</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1712,7 +1751,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1794,7 +1833,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1876,7 +1915,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1917,7 +1956,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1958,7 +1997,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G9" t="n">
         <v>580</v>
@@ -1999,7 +2038,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2181,7 +2220,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2208,7 +2247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,35 +2306,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·U.M.A闪耀ONLY（马娘only）</t>
+          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>东圃中山大道中358号 轰谧斯酒店</t>
+          <t>天河路299号B1层 天河时尚街</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>511</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>255</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80184</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n7B2YOEs1705908251849.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -2305,38 +2342,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>从化·FS动漫展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>天河路299号B1层 天河时尚街</t>
+          <t>从城大道383号 云岭湖酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>237</v>
+        <v>1610</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
         </is>
       </c>
     </row>
@@ -2351,33 +2388,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 13:30-02.03 15:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1593</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
         </is>
       </c>
     </row>
@@ -2392,33 +2429,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·怀旧ONLY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.03 10:00-02.03 16:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>847</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
         </is>
       </c>
     </row>
@@ -2428,38 +2465,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>841</v>
+        <v>252</v>
       </c>
       <c r="G6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -2474,33 +2511,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>239</v>
+        <v>1012</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -2510,38 +2547,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1000</v>
+        <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>380</v>
+        <v>63</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2593,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2570,19 +2607,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>1159</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -2592,38 +2629,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1147</v>
+        <v>768</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2670,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2648,23 +2685,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>749</v>
+        <v>803</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2679,33 +2716,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>795</v>
+        <v>1476</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2715,38 +2752,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1446</v>
+        <v>296</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2756,38 +2793,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>289</v>
+        <v>1040</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2802,33 +2839,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1035</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2838,38 +2875,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2884,33 +2921,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G17" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2925,33 +2962,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2966,33 +3003,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>490</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3007,33 +3044,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>473</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3085,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3062,19 +3099,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3089,33 +3126,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3162,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3171,33 +3208,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>274</v>
       </c>
       <c r="G24" t="n">
-        <v>35</v>
+        <v>288</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3212,33 +3249,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>268</v>
-      </c>
-      <c r="G25" t="n">
-        <v>288</v>
+        <v>115</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3248,40 +3287,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>114</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3291,38 +3328,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>297</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3332,38 +3369,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3429,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G29" t="n">
         <v>380</v>
@@ -3419,33 +3456,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>145</v>
+        <v>563</v>
       </c>
       <c r="G30" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3492,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3470,23 +3507,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3501,33 +3538,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3542,33 +3579,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>759</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3583,33 +3620,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>246</v>
+        <v>764</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3619,38 +3656,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="G35" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3660,38 +3697,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3706,33 +3743,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>587</v>
+        <v>187</v>
       </c>
       <c r="G37" t="n">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3742,38 +3779,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="G38" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3839,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -3824,38 +3861,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="G40" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3865,38 +3902,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>370</v>
+        <v>13</v>
       </c>
       <c r="G41" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3906,36 +3943,77 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>372</v>
+      </c>
+      <c r="G42" t="n">
+        <v>69</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F43" t="n">
         <v>6</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G43" t="n">
         <v>280</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="G3" t="n">
         <v>75</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>35</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G9" t="n">
         <v>580</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
         <v>63</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G16" t="n">
         <v>48.8</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>35</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G24" t="n">
         <v>288</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
         <v>78</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G29" t="n">
         <v>380</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G32" t="n">
         <v>68.8</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="G34" t="n">
         <v>39</v>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G38" t="n">
         <v>580</v>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G40" t="n">
         <v>380</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1615</v>
+        <v>1641</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="G3" t="n">
         <v>75</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1166</v>
+        <v>1180</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>35</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1591,36 +1591,79 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>372</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F30" t="n">
+        <v>374</v>
+      </c>
+      <c r="G30" t="n">
         <v>69</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1710,7 +1753,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1751,7 +1794,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1792,7 +1835,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
         <v>420</v>
@@ -1833,7 +1876,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1874,7 +1917,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1915,7 +1958,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1956,7 +1999,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1997,7 +2040,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G9" t="n">
         <v>580</v>
@@ -2038,7 +2081,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2120,7 +2163,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>280</v>
@@ -2220,7 +2263,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2247,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2320,7 +2363,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2361,7 +2404,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1615</v>
+        <v>1641</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -2402,7 +2445,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -2443,7 +2486,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -2484,7 +2527,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2525,7 +2568,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2566,7 +2609,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G8" t="n">
         <v>63</v>
@@ -2607,7 +2650,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1166</v>
+        <v>1180</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2648,7 +2691,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2689,7 +2732,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -2730,7 +2773,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2771,7 +2814,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2812,7 +2855,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2894,7 +2937,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
         <v>48.8</v>
@@ -2935,7 +2978,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -2976,7 +3019,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -3017,7 +3060,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3058,10 +3101,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3099,7 +3142,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -3140,7 +3183,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
         <v>420</v>
@@ -3181,7 +3224,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>35</v>
@@ -3222,7 +3265,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G24" t="n">
         <v>288</v>
@@ -3306,7 +3349,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3347,7 +3390,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
         <v>78</v>
@@ -3388,7 +3431,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3429,7 +3472,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G29" t="n">
         <v>380</v>
@@ -3470,7 +3513,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3511,7 +3554,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3552,7 +3595,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
         <v>68.8</v>
@@ -3593,7 +3636,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -3634,7 +3677,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="G34" t="n">
         <v>39</v>
@@ -3675,7 +3718,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3716,7 +3759,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -3757,7 +3800,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3798,7 +3841,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G38" t="n">
         <v>580</v>
@@ -3839,7 +3882,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -3880,7 +3923,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G40" t="n">
         <v>380</v>
@@ -3902,38 +3945,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
-      </c>
-      <c r="G41" t="n">
-        <v>64</v>
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3943,38 +3988,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>372</v>
+        <v>13</v>
       </c>
       <c r="G42" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3984,36 +4029,77 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>374</v>
+      </c>
+      <c r="G43" t="n">
+        <v>69</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="n">
         <v>280</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1641</v>
+        <v>1662</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="G3" t="n">
         <v>75</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1517</v>
+        <v>1539</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
         <v>35</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G30" t="n">
         <v>69</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="G3" t="n">
         <v>380</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G5" t="n">
         <v>288</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G9" t="n">
         <v>580</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
         <v>64</v>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1641</v>
+        <v>1662</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1517</v>
+        <v>1539</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
         <v>48.8</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
         <v>35</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G24" t="n">
         <v>288</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" t="n">
         <v>78</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G29" t="n">
         <v>380</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G32" t="n">
         <v>68.8</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="G34" t="n">
         <v>39</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G38" t="n">
         <v>580</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G40" t="n">
         <v>380</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
         <v>64</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G43" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1662</v>
+        <v>280</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>866</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>274</v>
+        <v>1201</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>830</v>
       </c>
       <c r="G5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1188</v>
+        <v>861</v>
       </c>
       <c r="G6" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>810</v>
+        <v>1571</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>831</v>
+        <v>321</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1539</v>
+        <v>1069</v>
       </c>
       <c r="G9" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>309</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1062</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>209</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>205</v>
+        <v>532</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,33 +1020,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,33 +1061,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>516</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1138,38 +1138,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
-      </c>
-      <c r="G18" t="n">
-        <v>55</v>
+        <v>114</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1179,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>302</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1220,40 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>115</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>591</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>302</v>
+        <v>590</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>581</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>584</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>57</v>
+        <v>790</v>
       </c>
       <c r="G24" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,33 +1432,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>266</v>
       </c>
       <c r="G25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>783</v>
+        <v>206</v>
       </c>
       <c r="G26" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>262</v>
-      </c>
-      <c r="G27" t="n">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,120 +1552,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>196</v>
+        <v>379</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>376</v>
-      </c>
-      <c r="G30" t="n">
-        <v>69</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1680,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,38 +1652,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>1047</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -1775,38 +1693,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1038</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -1816,38 +1734,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>288</v>
       </c>
       <c r="G4" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1857,38 +1775,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>283</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1898,38 +1816,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="G6" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,38 +1857,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -1980,38 +1898,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>600</v>
       </c>
       <c r="G8" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2021,38 +1939,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>599</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2062,38 +1980,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -2103,77 +2021,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>280</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2263,7 +2140,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2290,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2363,7 +2240,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2385,38 +2262,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>从化·FS动漫展</t>
+          <t>广州·原神x星铁x崩坏ONLY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>从城大道383号 云岭湖酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1662</v>
+        <v>280</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77976</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/z2IAZVfI1698830153507.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2303,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州·《数码宝贝:游乐园之谜》正版授权实景数码宝贝冒险舞台剧 </t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 15:30</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>1047</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81020</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8eR496991705559231218.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2344,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·怀旧ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 广州市岭南国际电子商务会展中心</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 16:30</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>866</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Ct8POYAX1704185345057.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2385,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>274</v>
+        <v>1201</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,38 +2426,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1038</v>
+        <v>830</v>
       </c>
       <c r="G7" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2467,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>861</v>
       </c>
       <c r="G8" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2631,38 +2508,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1188</v>
+        <v>1571</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2672,38 +2549,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>810</v>
+        <v>321</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2713,38 +2590,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>831</v>
+        <v>1069</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,38 +2631,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1539</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2795,38 +2672,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2836,38 +2713,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1062</v>
+        <v>209</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,38 +2754,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2923,33 +2800,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>532</v>
       </c>
       <c r="G16" t="n">
-        <v>48.8</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2964,33 +2841,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,33 +2882,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,33 +2923,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3082,38 +2959,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3123,38 +3000,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>288</v>
       </c>
       <c r="G21" t="n">
-        <v>55</v>
+        <v>288</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3164,38 +3041,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
-      </c>
-      <c r="G22" t="n">
-        <v>420</v>
+        <v>114</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3205,38 +3084,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>302</v>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3246,38 +3125,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>283</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3287,40 +3166,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>115</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>186</v>
+      </c>
+      <c r="G25" t="n">
+        <v>380</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3207,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>302</v>
+        <v>186</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3248,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>591</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3289,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="G28" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3330,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="G29" t="n">
-        <v>380</v>
+        <v>68.8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3371,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>581</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3412,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>584</v>
+        <v>790</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3453,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>57</v>
+        <v>266</v>
       </c>
       <c r="G32" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3494,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="G33" t="n">
-        <v>55</v>
+        <v>380</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3658,38 +3535,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>783</v>
+        <v>206</v>
       </c>
       <c r="G34" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3576,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>262</v>
+        <v>600</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3617,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3658,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>196</v>
+        <v>95</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3699,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>599</v>
-      </c>
-      <c r="G38" t="n">
-        <v>580</v>
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3742,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3783,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>91</v>
+        <v>379</v>
       </c>
       <c r="G40" t="n">
-        <v>380</v>
+        <v>69</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,161 +3824,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>280</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>人民北路696号 广州友谊剧院</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>14</v>
-      </c>
-      <c r="G42" t="n">
-        <v>64</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>376</v>
-      </c>
-      <c r="G43" t="n">
-        <v>69</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>7</v>
-      </c>
-      <c r="G44" t="n">
-        <v>280</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1571</v>
+        <v>1582</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
         <v>35</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="G24" t="n">
         <v>39</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G28" t="n">
         <v>69</v>
@@ -1671,10 +1671,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="G2" t="n">
-        <v>380</v>
+        <v>1051</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1712,7 +1714,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
         <v>420</v>
@@ -1753,7 +1755,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1835,7 +1837,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="G6" t="n">
         <v>380</v>
@@ -1876,7 +1878,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1917,7 +1919,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G8" t="n">
         <v>580</v>
@@ -1958,7 +1960,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -2040,7 +2042,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>280</v>
@@ -2140,7 +2142,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2240,7 +2242,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2281,10 +2283,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2322,10 +2324,12 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1047</v>
-      </c>
-      <c r="G4" t="n">
-        <v>380</v>
+        <v>1051</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2363,7 +2367,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -2404,7 +2408,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="G6" t="n">
         <v>63</v>
@@ -2445,7 +2449,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2486,7 +2490,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -2527,7 +2531,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1571</v>
+        <v>1582</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -2568,7 +2572,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2609,7 +2613,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -2650,7 +2654,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -2691,7 +2695,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -2732,7 +2736,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -2773,7 +2777,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -2814,7 +2818,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2855,7 +2859,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2896,7 +2900,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -2937,7 +2941,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>420</v>
@@ -2978,7 +2982,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -3019,7 +3023,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G21" t="n">
         <v>288</v>
@@ -3103,7 +3107,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3185,7 +3189,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="G25" t="n">
         <v>380</v>
@@ -3226,7 +3230,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3267,7 +3271,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3308,7 +3312,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3349,7 +3353,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3390,7 +3394,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -3431,7 +3435,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="G31" t="n">
         <v>39</v>
@@ -3472,7 +3476,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3513,7 +3517,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G33" t="n">
         <v>380</v>
@@ -3554,7 +3558,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3595,7 +3599,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G35" t="n">
         <v>580</v>
@@ -3636,7 +3640,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -3677,7 +3681,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -3802,7 +3806,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G40" t="n">
         <v>69</v>
@@ -3843,7 +3847,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>280</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>291</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>1216</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1207</v>
+        <v>855</v>
       </c>
       <c r="G4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -620,23 +620,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>867</v>
+        <v>1607</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1582</v>
+        <v>338</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>325</v>
+        <v>1093</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1081</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="G11" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>566</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>545</v>
+        <v>97</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1102,33 +1102,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" t="n">
-        <v>35</v>
+        <v>114</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1138,40 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>307</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="G24" t="n">
         <v>39</v>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,40 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>214</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1552,36 +1550,77 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>58</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>382</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F29" t="n">
+        <v>385</v>
+      </c>
+      <c r="G29" t="n">
         <v>69</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1671,7 +1710,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1755,7 +1794,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1796,7 +1835,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
@@ -1837,7 +1876,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G6" t="n">
         <v>380</v>
@@ -1919,10 +1958,12 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>602</v>
-      </c>
-      <c r="G8" t="n">
-        <v>580</v>
+        <v>607</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1960,7 +2001,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -2142,7 +2183,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2169,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2242,7 +2283,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2269,33 +2310,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·原神x星铁x崩坏ONLY</t>
+          <t>广州·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>革新路124号 太古仓码头</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 12:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>291</v>
-      </c>
-      <c r="G3" t="n">
-        <v>70</v>
+        <v>1055</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81073</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z160zins1705635411945.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
         </is>
       </c>
     </row>
@@ -2305,40 +2348,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1051</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>92</v>
+      </c>
+      <c r="G4" t="n">
+        <v>63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2394,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2367,19 +2408,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>1216</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2430,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1207</v>
+        <v>855</v>
       </c>
       <c r="G6" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2471,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2445,23 +2486,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2476,33 +2517,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>867</v>
+        <v>1607</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2553,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1582</v>
+        <v>338</v>
       </c>
       <c r="G9" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2553,38 +2594,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>325</v>
+        <v>1093</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,33 +2640,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1081</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2635,38 +2676,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2681,33 +2722,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="G13" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2722,33 +2763,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2763,33 +2804,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>566</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2804,33 +2845,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>545</v>
+        <v>97</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2886,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2859,19 +2900,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -2886,33 +2927,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2922,38 +2963,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -2968,33 +3009,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>297</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>288</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,33 +3050,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>291</v>
-      </c>
-      <c r="G21" t="n">
-        <v>288</v>
+        <v>114</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3045,40 +3088,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>114</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>307</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3088,38 +3129,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>304</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3170,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3230,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G25" t="n">
         <v>380</v>
@@ -3216,33 +3257,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>380</v>
+        <v>68.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3312,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3312,7 +3353,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3353,7 +3394,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3394,7 +3435,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -3435,7 +3476,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="G31" t="n">
         <v>39</v>
@@ -3544,33 +3585,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3585,33 +3626,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>602</v>
+        <v>214</v>
       </c>
       <c r="G35" t="n">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3621,38 +3662,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>96</v>
-      </c>
-      <c r="G36" t="n">
-        <v>380</v>
+        <v>607</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3724,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -3703,40 +3746,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>99</v>
+      </c>
+      <c r="G38" t="n">
+        <v>380</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3746,38 +3787,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3787,38 +3828,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>382</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3828,36 +3869,77 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>385</v>
+      </c>
+      <c r="G41" t="n">
+        <v>69</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F42" t="n">
         <v>8</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G42" t="n">
         <v>280</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1607</v>
+        <v>1628</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
         <v>68.8</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="G24" t="n">
         <v>39</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G29" t="n">
         <v>69</v>
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1691,40 +1691,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1055</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>420</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -1734,38 +1732,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>299</v>
       </c>
       <c r="G3" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1775,38 +1773,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1816,38 +1814,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="G5" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -1857,38 +1855,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="G6" t="n">
         <v>380</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -1898,38 +1896,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>380</v>
+        <v>607</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,40 +1939,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>607</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="G8" t="n">
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -1982,38 +1980,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -2023,77 +2021,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" t="n">
-        <v>280</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2183,7 +2140,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2210,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,7 +2240,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2305,40 +2262,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·次元LAB 二次元电音节</t>
+          <t>广州 · 原神x星穹铁道Only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>革新路124号 太古仓码头</t>
+          <t>钟落潭镇 越秀·白云·星汇城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 12:30-02.04 21:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1055</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>96</v>
+      </c>
+      <c r="G3" t="n">
+        <v>63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80147</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CNvZoKFi1703244154800.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2308,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·EY动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2367,19 +2322,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>92</v>
+        <v>1226</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2344,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1216</v>
+        <v>866</v>
       </c>
       <c r="G5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2385,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2445,23 +2400,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>855</v>
+        <v>894</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2476,33 +2431,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>880</v>
+        <v>1628</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2467,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1607</v>
+        <v>344</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2553,38 +2508,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>338</v>
+        <v>1101</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,33 +2554,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1093</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2635,38 +2590,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2681,33 +2636,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>228</v>
       </c>
       <c r="G12" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2722,33 +2677,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2763,33 +2718,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>573</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2804,33 +2759,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>566</v>
+        <v>101</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2800,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2859,19 +2814,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -2886,33 +2841,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2922,38 +2877,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -2968,33 +2923,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>299</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>288</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,33 +2964,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>297</v>
-      </c>
-      <c r="G20" t="n">
-        <v>288</v>
+        <v>114</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3045,40 +3002,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>114</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>310</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3088,38 +3043,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3084,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3144,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -3216,33 +3171,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>213</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>380</v>
+        <v>68.8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3257,33 +3212,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>613</v>
       </c>
       <c r="G26" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3293,38 +3248,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3339,33 +3294,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>596</v>
+        <v>90</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3375,38 +3330,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
-        <v>68.8</v>
+        <v>55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3421,33 +3376,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>814</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3462,33 +3417,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>804</v>
+        <v>276</v>
       </c>
       <c r="G31" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3498,38 +3453,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>270</v>
+        <v>77</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3539,38 +3494,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3585,33 +3540,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
       <c r="G34" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3626,33 +3581,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>214</v>
-      </c>
-      <c r="G35" t="n">
-        <v>60</v>
+        <v>607</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3662,40 +3619,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>607</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="G36" t="n">
+        <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3679,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -3746,38 +3701,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>380</v>
+        <v>58</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3787,38 +3742,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3828,38 +3783,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>387</v>
       </c>
       <c r="G40" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3869,77 +3824,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>385</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" t="n">
-        <v>280</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1226</v>
+        <v>1245</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>866</v>
+        <v>880</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1628</v>
+        <v>1652</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -897,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>573</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>101</v>
+        <v>592</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1102,35 +1102,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>114</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1138,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>310</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>312</v>
       </c>
       <c r="G19" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>613</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>612</v>
       </c>
       <c r="G22" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>68.8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>814</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,33 +1432,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>276</v>
+        <v>821</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="G26" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1528,19 +1528,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>219</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,36 +1591,159 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>广州·排球少年ONLY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>226</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>58</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>广州·潮娃展WWS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>西环路1号 广州岭南会展中心</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>48</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>387</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F32" t="n">
+        <v>390</v>
+      </c>
+      <c r="G32" t="n">
         <v>69</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1637,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1691,38 +1814,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -1732,38 +1855,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>299</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -1773,38 +1896,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1814,38 +1937,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>218</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -1855,38 +1978,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1896,40 +2019,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>607</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>223</v>
+      </c>
+      <c r="G7" t="n">
+        <v>380</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,38 +2060,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -1980,38 +2101,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" t="n">
-        <v>64</v>
+        <v>607</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2021,36 +2144,118 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.03.31 19:00-03.31 20:30</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>104</v>
+      </c>
+      <c r="G10" t="n">
+        <v>380</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G12" t="n">
         <v>280</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2140,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2167,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,7 +2445,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2281,7 +2486,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2322,7 +2527,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1226</v>
+        <v>1245</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2363,7 +2568,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>866</v>
+        <v>880</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2404,7 +2609,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2445,7 +2650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1628</v>
+        <v>1652</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2486,7 +2691,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2527,7 +2732,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2568,7 +2773,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2590,38 +2795,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>48.8</v>
+        <v>120</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -2636,33 +2841,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>228</v>
+        <v>93</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,33 +2882,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>239</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2718,33 +2923,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>573</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,33 +2964,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,33 +3005,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>592</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2841,33 +3046,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="G17" t="n">
-        <v>420</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,38 +3082,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -2918,38 +3123,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>299</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2964,35 +3169,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>114</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3002,38 +3205,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3043,38 +3246,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
-      </c>
-      <c r="G22" t="n">
-        <v>78</v>
+        <v>114</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3084,38 +3289,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>218</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3330,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>218</v>
+        <v>312</v>
       </c>
       <c r="G24" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3371,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>68.8</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3212,33 +3417,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>613</v>
+        <v>223</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3248,38 +3453,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>604</v>
+        <v>223</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3494,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3304,23 +3509,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="G28" t="n">
         <v>68.8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3535,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>622</v>
       </c>
       <c r="G29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3576,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>814</v>
+        <v>612</v>
       </c>
       <c r="G30" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3617,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3658,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3699,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>821</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3740,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,40 +3781,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>607</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="G35" t="n">
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3619,38 +3822,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3660,38 +3863,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3701,38 +3904,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3742,38 +3945,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
-      </c>
-      <c r="G39" t="n">
-        <v>64</v>
+        <v>607</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3783,38 +3988,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>387</v>
+        <v>104</v>
       </c>
       <c r="G40" t="n">
-        <v>69</v>
+        <v>380</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3824,36 +4029,241 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.03.31 19:00-03.31 20:30</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>104</v>
+      </c>
+      <c r="G41" t="n">
+        <v>380</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>58</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>广州·潮娃展WWS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>西环路1号 广州岭南会展中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>48</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>16</v>
+      </c>
+      <c r="G44" t="n">
+        <v>64</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>390</v>
+      </c>
+      <c r="G45" t="n">
+        <v>69</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F46" t="n">
         <v>8</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G46" t="n">
         <v>280</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>880</v>
+        <v>897</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1652</v>
+        <v>1671</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
         <v>63</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G23" t="n">
         <v>68.8</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="G25" t="n">
         <v>39</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>48</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G32" t="n">
         <v>69</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>64</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>880</v>
+        <v>897</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1652</v>
+        <v>1671</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G12" t="n">
         <v>48.8</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>63</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G21" t="n">
         <v>288</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>88</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G28" t="n">
         <v>68.8</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G31" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="G33" t="n">
         <v>39</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G35" t="n">
         <v>380</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>58</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
         <v>48</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
         <v>64</v>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G45" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1253</v>
+        <v>1272</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>928</v>
+        <v>945</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1671</v>
+        <v>1695</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>246</v>
+        <v>101</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>255</v>
       </c>
       <c r="G12" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>607</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,33 +1020,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>117</v>
+        <v>623</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,35 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="G18" t="n">
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1179,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>312</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
+        <v>115</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>314</v>
       </c>
       <c r="G20" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1268,33 +1268,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>629</v>
+        <v>87</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>68.8</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>621</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>825</v>
+        <v>121</v>
       </c>
       <c r="G25" t="n">
-        <v>39</v>
+        <v>68.8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>285</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>830</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>290</v>
       </c>
       <c r="G28" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1610,19 +1610,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1673,38 +1673,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="G31" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,36 +1714,118 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>58</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>广州·潮娃展WWS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>西环路1号 广州岭南会展中心</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>48</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>391</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F34" t="n">
+        <v>392</v>
+      </c>
+      <c r="G34" t="n">
         <v>69</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1760,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1915,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1956,10 +2038,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2038,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2079,7 +2161,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2101,40 +2183,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>609</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>75</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -2144,38 +2224,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
-      </c>
-      <c r="G10" t="n">
-        <v>380</v>
+        <v>611</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,38 +2267,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="G11" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2226,36 +2308,77 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>19</v>
+      </c>
+      <c r="G12" t="n">
+        <v>64</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>280</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2345,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2372,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2445,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2486,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2527,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1253</v>
+        <v>1272</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2568,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2609,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>928</v>
+        <v>945</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2650,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1671</v>
+        <v>1695</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2691,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2732,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2773,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2841,33 +2964,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -2882,33 +3005,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>246</v>
+        <v>101</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2923,33 +3046,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>255</v>
       </c>
       <c r="G14" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2964,33 +3087,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,33 +3128,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>607</v>
+        <v>76</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,33 +3169,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>117</v>
+        <v>623</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3210,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3101,19 +3224,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -3128,33 +3251,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G19" t="n">
-        <v>420</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3164,38 +3287,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>420</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3210,33 +3333,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>288</v>
+        <v>35</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3251,35 +3374,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>114</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>305</v>
+      </c>
+      <c r="G22" t="n">
+        <v>288</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3289,38 +3410,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>88</v>
+        <v>115</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3335,33 +3458,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>312</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3494,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3535,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3499,33 +3622,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="G28" t="n">
-        <v>68.8</v>
+        <v>380</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,33 +3663,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>629</v>
+        <v>87</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3699,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3740,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>68.8</v>
+        <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3658,38 +3781,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>621</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3822,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>825</v>
+        <v>121</v>
       </c>
       <c r="G33" t="n">
-        <v>39</v>
+        <v>68.8</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3745,33 +3868,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>285</v>
+        <v>27</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3904,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>80</v>
+        <v>830</v>
       </c>
       <c r="G35" t="n">
-        <v>380</v>
+        <v>39</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3945,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>47</v>
+        <v>290</v>
       </c>
       <c r="G36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3986,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="G37" t="n">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3904,38 +4027,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>236</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,35 +4073,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>609</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +4109,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="G40" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +4150,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>104</v>
+        <v>239</v>
       </c>
       <c r="G41" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,38 +4191,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="n">
-        <v>58</v>
+        <v>611</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -4111,38 +4234,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="G43" t="n">
-        <v>48</v>
+        <v>380</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4275,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="G44" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4316,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>391</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,36 +4357,159 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>广州·潮娃展WWS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>西环路1号 广州岭南会展中心</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2024.04.13 10:00-04.13 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>48</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>人民北路696号 广州友谊剧院</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.04.19 19:30-04.19 21:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>19</v>
+      </c>
+      <c r="G47" t="n">
+        <v>64</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>392</v>
+      </c>
+      <c r="G48" t="n">
+        <v>69</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F49" t="n">
         <v>8</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G49" t="n">
         <v>280</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1695</v>
+        <v>1708</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>58</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1695</v>
+        <v>1708</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
         <v>35</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
         <v>78</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
         <v>58</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" t="n">
         <v>64</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1278</v>
+        <v>1287</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>954</v>
+        <v>971</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1708</v>
+        <v>1729</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>120</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
         <v>280</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1278</v>
+        <v>1287</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>954</v>
+        <v>971</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1708</v>
+        <v>1729</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>120</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
         <v>35</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
         <v>118</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
         <v>78</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
         <v>280</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1729</v>
+        <v>1740</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1147</v>
+        <v>1161</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1729</v>
+        <v>1740</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1147</v>
+        <v>1161</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>935</v>
+        <v>1031</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1740</v>
+        <v>1759</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>385</v>
+        <v>477</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>58</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>935</v>
+        <v>1031</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1740</v>
+        <v>1759</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>385</v>
+        <v>477</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
         <v>58</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G47" t="n">
         <v>64</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1031</v>
+        <v>1106</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1759</v>
+        <v>1765</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>477</v>
+        <v>547</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
         <v>58</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2495,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1031</v>
+        <v>1106</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1759</v>
+        <v>1765</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>477</v>
+        <v>547</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
         <v>35</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>118</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4275,38 +4275,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>380</v>
+        <v>58</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4335,19 +4335,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4357,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G46" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -4398,38 +4398,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="G47" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -4439,77 +4439,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>404</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>9</v>
-      </c>
-      <c r="G49" t="n">
-        <v>280</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1303</v>
+        <v>1318</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1765</v>
+        <v>1781</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>280</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1303</v>
+        <v>1318</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1765</v>
+        <v>1781</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
         <v>118</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
         <v>280</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2495,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>35</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
         <v>118</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4275,38 +4275,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="G44" t="n">
-        <v>58</v>
+        <v>380</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4335,19 +4335,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G45" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4357,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -4398,38 +4398,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="G47" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -4439,36 +4439,77 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>同泰路颐和山庄 颐和大酒店</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.20 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>404</v>
+      </c>
+      <c r="G48" t="n">
+        <v>69</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>2024-04-28</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>11</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G49" t="n">
         <v>280</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
         <v>35</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>118</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
         <v>58</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
         <v>118</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
         <v>78</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
         <v>58</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1332</v>
+        <v>1344</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1137</v>
+        <v>1152</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1026</v>
+        <v>1044</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1805</v>
+        <v>1829</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
         <v>58</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1332</v>
+        <v>1343</v>
       </c>
       <c r="G4" t="n">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1137</v>
+        <v>1152</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1026</v>
+        <v>1044</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1805</v>
+        <v>1829</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
         <v>35</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
         <v>78</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G31" t="n">
         <v>58</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G47" t="n">
         <v>64</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G2" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="G3" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1829</v>
+        <v>1838</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
         <v>58</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
         <v>55</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="G27" t="n">
         <v>39</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G34" t="n">
         <v>69</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G3" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="G4" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1829</v>
+        <v>1838</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G15" t="n">
         <v>63</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G22" t="n">
         <v>288</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
         <v>78</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G27" t="n">
         <v>380</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
         <v>58</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G33" t="n">
         <v>68.8</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="G35" t="n">
         <v>39</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G47" t="n">
         <v>64</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G48" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>151</v>
+        <v>1165</v>
       </c>
       <c r="G2" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1347</v>
+        <v>1071</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1157</v>
+        <v>1867</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1050</v>
+        <v>588</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1838</v>
+        <v>1229</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>584</v>
+        <v>63</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1222</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="G11" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>313</v>
+        <v>95</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>90</v>
+        <v>764</v>
       </c>
       <c r="G13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,33 +1020,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>732</v>
+        <v>118</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>111</v>
-      </c>
-      <c r="G17" t="n">
-        <v>55</v>
+        <v>115</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1138,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1179,40 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>115</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>188</v>
+      </c>
+      <c r="G19" t="n">
+        <v>68.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>334</v>
+        <v>688</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1268,33 +1268,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="G23" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>655</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>171</v>
+        <v>890</v>
       </c>
       <c r="G25" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="G26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>888</v>
+        <v>177</v>
       </c>
       <c r="G27" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>329</v>
+        <v>53</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1610,19 +1610,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1673,38 +1673,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,118 +1714,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>416</v>
       </c>
       <c r="G32" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>广州·潮娃展WWS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>西环路1号 广州岭南会展中心</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>19</v>
-      </c>
-      <c r="G33" t="n">
-        <v>48</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>413</v>
-      </c>
-      <c r="G34" t="n">
-        <v>69</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1997,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2038,7 +1956,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -2286,7 +2204,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2468,7 +2386,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2495,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,7 +2486,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2590,38 +2508,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州 · 原神x星穹铁道Only</t>
+          <t>广州·运动番only4.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>151</v>
+        <v>1165</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81331</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/RMPUzrbI1706077790086.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
         </is>
       </c>
     </row>
@@ -2631,38 +2549,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·EY动漫嘉年华</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>钟落潭镇 越秀·白云·星汇城</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1347</v>
+        <v>1071</v>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MMh15Yoz1704700792562.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2672,38 +2590,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1157</v>
+        <v>1867</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2713,38 +2631,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1050</v>
+        <v>588</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,38 +2672,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1838</v>
+        <v>1229</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2795,38 +2713,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>584</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2836,38 +2754,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1222</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -2877,38 +2795,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -2918,38 +2836,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.23 20:30-02.24 02:30</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2964,33 +2882,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,33 +2923,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="G13" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,33 +2964,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>313</v>
+        <v>95</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -3087,33 +3005,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>764</v>
       </c>
       <c r="G15" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3128,33 +3046,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -3169,33 +3087,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>732</v>
+        <v>118</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3210,33 +3128,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3246,38 +3164,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3287,38 +3205,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>327</v>
       </c>
       <c r="G20" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3333,33 +3251,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
-      </c>
-      <c r="G21" t="n">
-        <v>35</v>
+        <v>115</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3369,38 +3289,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>324</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>288</v>
+        <v>118</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -3410,40 +3330,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>115</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>336</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3371,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3412,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3453,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>263</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,33 +3499,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="G27" t="n">
-        <v>380</v>
+        <v>68.8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3622,33 +3540,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>263</v>
+        <v>688</v>
       </c>
       <c r="G28" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,33 +3581,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="G29" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3617,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3658,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="G31" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3699,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>655</v>
+        <v>41</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3740,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>171</v>
+        <v>890</v>
       </c>
       <c r="G33" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3868,33 +3786,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3822,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>888</v>
+        <v>82</v>
       </c>
       <c r="G35" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3863,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>329</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3904,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="G37" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +3945,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -4073,12 +3991,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4087,19 +4005,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="G39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -4114,33 +4032,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>53</v>
-      </c>
-      <c r="G40" t="n">
-        <v>68</v>
+        <v>621</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -4150,38 +4070,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>289</v>
+        <v>125</v>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4191,40 +4111,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>621</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="G42" t="n">
+        <v>380</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4152,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="G43" t="n">
-        <v>380</v>
+        <v>58</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4193,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
-        <v>380</v>
+        <v>48</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,38 +4234,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G45" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4275,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="G46" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -4398,118 +4316,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>413</v>
-      </c>
-      <c r="G48" t="n">
-        <v>69</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>11</v>
-      </c>
-      <c r="G49" t="n">
-        <v>280</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1867</v>
+        <v>1884</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G9" t="n">
         <v>48.8</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G19" t="n">
         <v>68.8</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
         <v>58</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G23" t="n">
         <v>68.8</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
         <v>55</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="G25" t="n">
         <v>39</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G32" t="n">
         <v>69</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1867</v>
+        <v>1884</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G20" t="n">
         <v>288</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
         <v>118</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G27" t="n">
         <v>68.8</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G31" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="G33" t="n">
         <v>39</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="n">
         <v>380</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G37" t="n">
         <v>65</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G38" t="n">
         <v>68</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G41" t="n">
         <v>380</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G42" t="n">
         <v>380</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G46" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1884</v>
+        <v>1909</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1232</v>
+        <v>1243</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
         <v>48.8</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
         <v>35</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="G19" t="n">
         <v>68.8</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G21" t="n">
         <v>58</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G23" t="n">
         <v>68.8</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G24" t="n">
         <v>55</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="G25" t="n">
         <v>39</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G32" t="n">
         <v>69</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
         <v>420</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1884</v>
+        <v>1909</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1232</v>
+        <v>1243</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
         <v>420</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
         <v>35</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G20" t="n">
         <v>288</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
         <v>118</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="G27" t="n">
         <v>68.8</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G31" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="G33" t="n">
         <v>39</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G37" t="n">
         <v>65</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G38" t="n">
         <v>68</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G41" t="n">
         <v>380</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G42" t="n">
         <v>380</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
         <v>58</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G46" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1909</v>
+        <v>1923</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1243</v>
+        <v>1253</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G19" t="n">
         <v>68.8</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G21" t="n">
         <v>58</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G23" t="n">
         <v>68.8</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" t="n">
         <v>55</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="G25" t="n">
         <v>39</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
         <v>48</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G32" t="n">
         <v>69</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1909</v>
+        <v>1923</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1243</v>
+        <v>1253</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G13" t="n">
         <v>63</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="G15" t="n">
         <v>68</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G20" t="n">
         <v>288</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G25" t="n">
         <v>380</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G27" t="n">
         <v>68.8</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G31" t="n">
         <v>68.8</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="G33" t="n">
         <v>39</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G37" t="n">
         <v>65</v>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G44" t="n">
         <v>48</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G46" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,12 +482,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -497,23 +497,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1180</v>
+        <v>1138</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1114</v>
+        <v>1956</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1923</v>
+        <v>615</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>598</v>
+        <v>1266</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1253</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>136</v>
+        <v>341</v>
       </c>
       <c r="G9" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>330</v>
+        <v>123</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G11" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>98</v>
+        <v>836</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>817</v>
+        <v>256</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
-      </c>
-      <c r="G16" t="n">
-        <v>35</v>
+        <v>116</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1097,40 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>116</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>346</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>342</v>
+        <v>247</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>226</v>
+        <v>707</v>
       </c>
       <c r="G19" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>696</v>
+        <v>80</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1278,23 +1278,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>74</v>
+        <v>671</v>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>665</v>
+        <v>202</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>68.8</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>912</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>906</v>
+        <v>367</v>
       </c>
       <c r="G25" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>354</v>
+        <v>197</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="G28" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>303</v>
+        <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,17 +1632,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1651,19 +1651,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -1673,77 +1673,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="G31" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>423</v>
-      </c>
-      <c r="G32" t="n">
-        <v>69</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1814,7 +1773,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1855,7 +1814,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1896,7 +1855,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1915,7 +1874,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1937,7 +1896,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1978,7 +1937,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1997,7 +1956,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2019,7 +1978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2060,7 +2019,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2101,7 +2060,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2142,7 +2101,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2161,7 +2120,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2185,7 +2144,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024.03.31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2204,7 +2163,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2226,7 +2185,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2245,7 +2204,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2267,7 +2226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024.04.28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2367,7 +2326,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024.02.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2386,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2413,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2467,7 +2426,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024.02.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2486,7 +2445,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2508,12 +2467,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·运动番only4.0</t>
+          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2523,23 +2482,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 16:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1180</v>
+        <v>1138</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80499</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/PIe3tyn61705383800643.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,38 +2508,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1114</v>
+        <v>1956</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2549,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1923</v>
+        <v>615</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2631,38 +2590,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>598</v>
+        <v>1266</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2672,38 +2631,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1253</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2713,38 +2672,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -2754,38 +2713,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.23 20:30-02.24 02:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -2795,38 +2754,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2836,38 +2795,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>136</v>
+        <v>341</v>
       </c>
       <c r="G11" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,38 +2836,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>330</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -2918,38 +2877,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2959,38 +2918,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>98</v>
+        <v>836</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -3000,38 +2959,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>817</v>
+        <v>256</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3000,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3060,19 +3019,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3082,38 +3041,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3123,38 +3082,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3164,38 +3123,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>334</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>288</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3205,38 +3164,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>333</v>
-      </c>
-      <c r="G20" t="n">
-        <v>288</v>
+        <v>116</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3246,40 +3207,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>116</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>118</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -3289,38 +3248,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="G22" t="n">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3289,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>342</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3330,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3371,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="G25" t="n">
-        <v>380</v>
+        <v>68.8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3412,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>265</v>
+        <v>707</v>
       </c>
       <c r="G26" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3453,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="G27" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3494,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3535,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3576,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>665</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3658,38 +3617,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>191</v>
+        <v>912</v>
       </c>
       <c r="G31" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3658,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>48</v>
+        <v>367</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3699,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>906</v>
+        <v>83</v>
       </c>
       <c r="G33" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3740,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>354</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3781,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="G35" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3822,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,17 +3863,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3923,19 +3882,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>190</v>
+        <v>307</v>
       </c>
       <c r="G37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3904,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>58</v>
-      </c>
-      <c r="G38" t="n">
-        <v>68</v>
+        <v>623</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3947,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>303</v>
+        <v>130</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,40 +3988,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>622</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="G40" t="n">
+        <v>58</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,38 +4029,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="G41" t="n">
-        <v>380</v>
+        <v>48</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -4111,38 +4070,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="G42" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4111,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G43" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,159 +4152,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>人民北路696号 广州友谊剧院</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>25</v>
-      </c>
-      <c r="G45" t="n">
-        <v>64</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>423</v>
-      </c>
-      <c r="G46" t="n">
-        <v>69</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>11</v>
-      </c>
-      <c r="G47" t="n">
-        <v>280</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1138</v>
+        <v>1156</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1956</v>
+        <v>1969</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G8" t="n">
         <v>48.8</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>836</v>
+        <v>858</v>
       </c>
       <c r="G12" t="n">
         <v>68</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
         <v>35</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G18" t="n">
         <v>68.8</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G20" t="n">
         <v>58</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="G24" t="n">
         <v>39</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G31" t="n">
         <v>69</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1138</v>
+        <v>1156</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1956</v>
+        <v>1969</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
         <v>63</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>836</v>
+        <v>858</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G19" t="n">
         <v>288</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
         <v>118</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="G31" t="n">
         <v>39</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
         <v>68</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G42" t="n">
         <v>64</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G43" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1156</v>
+        <v>1181</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1969</v>
+        <v>1997</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G8" t="n">
         <v>48.8</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="G12" t="n">
         <v>68</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
         <v>35</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="G18" t="n">
         <v>68.8</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G20" t="n">
         <v>58</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="G24" t="n">
         <v>39</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
         <v>48</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G31" t="n">
         <v>69</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1156</v>
+        <v>1181</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1969</v>
+        <v>1997</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G12" t="n">
         <v>63</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
         <v>35</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G19" t="n">
         <v>288</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
         <v>118</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="G31" t="n">
         <v>39</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G36" t="n">
         <v>68</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
         <v>58</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G41" t="n">
         <v>48</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G42" t="n">
         <v>64</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G43" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="G2" t="n">
-        <v>58</v>
+        <v>1201</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +544,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G8" t="n">
         <v>48.8</v>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G10" t="n">
         <v>63</v>
@@ -870,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="G12" t="n">
         <v>68</v>
@@ -993,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1075,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1118,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="G18" t="n">
         <v>68.8</v>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G20" t="n">
         <v>58</v>
@@ -1282,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -1364,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="G24" t="n">
         <v>39</v>
@@ -1446,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1487,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1528,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1569,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1610,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G30" t="n">
         <v>48</v>
@@ -1692,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G31" t="n">
         <v>69</v>
@@ -1874,7 +1876,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1915,7 +1917,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1956,7 +1958,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1997,7 +1999,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2079,7 +2081,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2163,7 +2165,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2204,7 +2206,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2345,7 +2347,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2445,7 +2447,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2486,10 +2488,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1181</v>
-      </c>
-      <c r="G3" t="n">
-        <v>58</v>
+        <v>1201</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2527,10 +2531,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2568,7 +2572,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2609,7 +2613,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2732,7 +2736,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2773,7 +2777,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -2814,7 +2818,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -2855,7 +2859,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G12" t="n">
         <v>63</v>
@@ -2896,7 +2900,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2937,7 +2941,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -3019,7 +3023,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3142,7 +3146,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G19" t="n">
         <v>288</v>
@@ -3183,7 +3187,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3226,7 +3230,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
         <v>118</v>
@@ -3267,7 +3271,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3308,7 +3312,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -3349,7 +3353,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -3390,7 +3394,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="G25" t="n">
         <v>68.8</v>
@@ -3431,7 +3435,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3472,7 +3476,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -3513,7 +3517,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3554,7 +3558,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G29" t="n">
         <v>68.8</v>
@@ -3595,7 +3599,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -3636,7 +3640,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="G31" t="n">
         <v>39</v>
@@ -3677,7 +3681,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3759,7 +3763,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -3800,7 +3804,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -3841,7 +3845,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G36" t="n">
         <v>68</v>
@@ -3882,7 +3886,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3966,7 +3970,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G39" t="n">
         <v>380</v>
@@ -4007,7 +4011,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G40" t="n">
         <v>58</v>
@@ -4048,7 +4052,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G41" t="n">
         <v>48</v>
@@ -4089,7 +4093,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G42" t="n">
         <v>64</v>
@@ -4130,7 +4134,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G43" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,35 +487,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1201</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>2034</v>
+      </c>
+      <c r="G2" t="n">
+        <v>68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2014</v>
+        <v>652</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>638</v>
+        <v>1300</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -612,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1290</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -648,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -735,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>146</v>
+        <v>368</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>362</v>
+        <v>154</v>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -858,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>114</v>
+        <v>932</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -899,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>897</v>
+        <v>290</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,12 +938,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -954,19 +952,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1020,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
-      </c>
-      <c r="G15" t="n">
-        <v>35</v>
+        <v>119</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -1058,40 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>119</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>353</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>350</v>
+        <v>313</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1147,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>288</v>
+        <v>730</v>
       </c>
       <c r="G18" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1186,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1202,19 +1200,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>722</v>
+        <v>109</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1222,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1239,23 +1237,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>689</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1268,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>682</v>
+        <v>229</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>220</v>
+        <v>59</v>
       </c>
       <c r="G22" t="n">
-        <v>68.8</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,33 +1350,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>53</v>
+        <v>946</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>938</v>
+        <v>402</v>
       </c>
       <c r="G24" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>391</v>
+        <v>222</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1475,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1516,33 +1514,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>66</v>
+        <v>333</v>
       </c>
       <c r="G27" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1552,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1596,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1612,19 +1610,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -1634,77 +1632,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>442</v>
       </c>
       <c r="G30" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>439</v>
-      </c>
-      <c r="G31" t="n">
-        <v>69</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1794,7 +1751,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>120</v>
@@ -1876,7 +1833,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1917,7 +1874,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1999,7 +1956,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2040,7 +1997,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2122,7 +2079,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2165,7 +2122,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2374,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,35 +2431,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州· 妖都原神only 2.0-提瓦特新春游园会</t>
+          <t>广州·樱漫动漫嘉年华8.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 16:30</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1201</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>2034</v>
+      </c>
+      <c r="G3" t="n">
+        <v>68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79914</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5TL7q6uK1702897965361.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2467,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·星火.AI动漫嘉年华3.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2014</v>
+        <v>652</v>
       </c>
       <c r="G4" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
         </is>
       </c>
     </row>
@@ -2553,38 +2508,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>638</v>
+        <v>1300</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,33 +2554,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1290</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2635,38 +2590,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -2676,38 +2631,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.23 20:30-02.24 02:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -2722,33 +2677,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2763,33 +2718,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>146</v>
+        <v>368</v>
       </c>
       <c r="G10" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2804,33 +2759,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>362</v>
+        <v>154</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -2845,33 +2800,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="G12" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2886,33 +2841,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>114</v>
+        <v>932</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2927,33 +2882,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>897</v>
+        <v>290</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2923,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2982,19 +2937,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,33 +2964,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>146</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -3045,38 +3000,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -3091,33 +3046,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>344</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>288</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3132,33 +3087,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>341</v>
-      </c>
-      <c r="G19" t="n">
-        <v>288</v>
+        <v>119</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3168,40 +3125,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>119</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="G20" t="n">
+        <v>118</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -3216,33 +3171,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="G21" t="n">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3252,38 +3207,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3293,38 +3248,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>273</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3339,33 +3294,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="G24" t="n">
-        <v>380</v>
+        <v>68.8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3380,33 +3335,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>288</v>
+        <v>730</v>
       </c>
       <c r="G25" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3376,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3435,19 +3390,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>722</v>
+        <v>109</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3412,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3472,23 +3427,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>101</v>
+        <v>689</v>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3503,33 +3458,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>682</v>
+        <v>229</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3539,38 +3494,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>220</v>
+        <v>59</v>
       </c>
       <c r="G29" t="n">
-        <v>68.8</v>
+        <v>55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3585,33 +3540,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>53</v>
+        <v>946</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3626,33 +3581,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>938</v>
+        <v>402</v>
       </c>
       <c r="G31" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3662,38 +3617,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3708,33 +3663,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -3744,38 +3699,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>222</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3790,33 +3745,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3831,33 +3786,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>66</v>
+        <v>333</v>
       </c>
       <c r="G36" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3872,33 +3827,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>321</v>
-      </c>
-      <c r="G37" t="n">
-        <v>60</v>
+        <v>625</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3908,40 +3865,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>623</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="G38" t="n">
+        <v>380</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3951,38 +3906,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.03.31</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="G39" t="n">
-        <v>380</v>
+        <v>58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3997,12 +3952,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4011,19 +3966,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G40" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -4033,38 +3988,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -4074,38 +4029,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024.04.19</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>30</v>
+        <v>442</v>
       </c>
       <c r="G42" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -4115,77 +4070,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>439</v>
+        <v>11</v>
       </c>
       <c r="G43" t="n">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024.04.28</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>11</v>
-      </c>
-      <c r="G44" t="n">
-        <v>280</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2034</v>
+        <v>2041</v>
       </c>
       <c r="G2" t="n">
         <v>68</v>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G7" t="n">
         <v>48.8</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="G11" t="n">
         <v>68</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
         <v>35</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G19" t="n">
         <v>58</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G21" t="n">
         <v>68.8</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="G23" t="n">
         <v>39</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G25" t="n">
         <v>65</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G30" t="n">
         <v>69</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2034</v>
+        <v>2041</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G9" t="n">
         <v>48.8</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
         <v>35</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G18" t="n">
         <v>288</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
         <v>118</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
         <v>78</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G23" t="n">
         <v>380</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G26" t="n">
         <v>58</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G28" t="n">
         <v>68.8</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
         <v>55</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="G30" t="n">
         <v>39</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G34" t="n">
         <v>65</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G35" t="n">
         <v>68</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G40" t="n">
         <v>48</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41" t="n">
         <v>64</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G42" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2041</v>
+        <v>1319</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>659</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1305</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G7" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>370</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>159</v>
+        <v>977</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>119</v>
+        <v>312</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>944</v>
+        <v>170</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>301</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>160</v>
-      </c>
-      <c r="G13" t="n">
-        <v>60</v>
+        <v>119</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -974,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>357</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,40 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>339</v>
+      </c>
+      <c r="G15" t="n">
+        <v>68.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>355</v>
+        <v>748</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>324</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>738</v>
+        <v>701</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>695</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>238</v>
+        <v>963</v>
       </c>
       <c r="G21" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>424</v>
+      </c>
+      <c r="G22" t="n">
         <v>60</v>
       </c>
-      <c r="G22" t="n">
-        <v>55</v>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>954</v>
+        <v>234</v>
       </c>
       <c r="G23" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>415</v>
+        <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1446,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>230</v>
+        <v>347</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>341</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,118 +1550,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024.04.13</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>广州·潮娃展WWS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>西环路1号 广州岭南会展中心</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>31</v>
-      </c>
-      <c r="G29" t="n">
-        <v>48</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>444</v>
-      </c>
-      <c r="G30" t="n">
-        <v>69</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1792,7 +1710,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>420</v>
@@ -1833,7 +1751,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1874,7 +1792,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1915,7 +1833,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1956,7 +1874,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2122,7 +2040,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2304,7 +2222,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2331,7 +2249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2404,7 +2322,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2426,38 +2344,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华8.0</t>
+          <t>广州·cooperative kingdom同人展2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>洛浦街夏滘西环路1号 岭南电商园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2041</v>
+        <v>1319</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/pxg3W5Hu1702536379071.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2385,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·星火.AI动漫嘉年华3.0</t>
+          <t>广州·明日方舟×桌游only茶会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迎宾路(沙溪路段)111号-3 美丽豪酒店(广州沙溪地铁站国际酒店用品城店)</t>
+          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>659</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80961</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Fm8iCNPM1705483173204.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2426,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1305</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -2549,38 +2467,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2508,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.23 20:30-02.24 02:30</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>48.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2636,33 +2554,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,33 +2595,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G9" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -2718,33 +2636,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>370</v>
+        <v>120</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,33 +2677,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>159</v>
+        <v>977</v>
       </c>
       <c r="G11" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,33 +2718,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>119</v>
+        <v>312</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -2841,33 +2759,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>944</v>
+        <v>170</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -2882,33 +2800,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2918,38 +2836,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -2959,38 +2877,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="G16" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,33 +2923,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G17" t="n">
-        <v>35</v>
+        <v>119</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -3041,38 +2961,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>347</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
-        <v>288</v>
+        <v>118</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -3082,40 +3002,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>119</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>357</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3043,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3084,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>355</v>
+        <v>277</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3207,38 +3125,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>339</v>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>68.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3253,33 +3171,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>274</v>
+        <v>748</v>
       </c>
       <c r="G23" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3294,33 +3212,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>324</v>
+        <v>124</v>
       </c>
       <c r="G24" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3248,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>738</v>
+        <v>701</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3289,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3330,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>695</v>
+        <v>62</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3371,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>238</v>
+        <v>963</v>
       </c>
       <c r="G28" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3499,33 +3417,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>424</v>
+      </c>
+      <c r="G29" t="n">
         <v>60</v>
       </c>
-      <c r="G29" t="n">
-        <v>55</v>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3453,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>954</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3494,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>415</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3535,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3658,38 +3576,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3622,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3718,19 +3636,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>230</v>
+        <v>347</v>
       </c>
       <c r="G34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,33 +3663,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>74</v>
-      </c>
-      <c r="G35" t="n">
-        <v>68</v>
+        <v>625</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3701,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>341</v>
+        <v>143</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,40 +3742,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>625</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="G37" t="n">
+        <v>58</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3865,38 +3783,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.03.31</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="G38" t="n">
-        <v>380</v>
+        <v>48</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -3906,38 +3824,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3947,38 +3865,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>31</v>
+        <v>448</v>
       </c>
       <c r="G40" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,118 +3906,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.19</t>
+          <t>2024.04.28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>444</v>
-      </c>
-      <c r="G42" t="n">
-        <v>69</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024.04.28</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>11</v>
-      </c>
-      <c r="G43" t="n">
-        <v>280</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>977</v>
+        <v>1007</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
         <v>35</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G15" t="n">
         <v>68.8</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G19" t="n">
         <v>68.8</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="G21" t="n">
         <v>39</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24" t="n">
         <v>68</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
         <v>58</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G28" t="n">
         <v>69</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G7" t="n">
         <v>48.8</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G9" t="n">
         <v>63</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>977</v>
+        <v>1007</v>
       </c>
       <c r="G11" t="n">
         <v>68</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
         <v>35</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G16" t="n">
         <v>288</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
         <v>118</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G22" t="n">
         <v>68.8</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G24" t="n">
         <v>58</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G26" t="n">
         <v>68.8</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="G28" t="n">
         <v>39</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G32" t="n">
         <v>65</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G33" t="n">
         <v>68</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G37" t="n">
         <v>58</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G38" t="n">
         <v>48</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G40" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1324</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>48.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G5" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>389</v>
+        <v>126</v>
       </c>
       <c r="G6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>175</v>
+        <v>1058</v>
       </c>
       <c r="G7" t="n">
-        <v>63</v>
+        <v>61.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>123</v>
+        <v>351</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1007</v>
+        <v>179</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>325</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>175</v>
-      </c>
-      <c r="G11" t="n">
-        <v>60</v>
+        <v>119</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -892,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>364</v>
       </c>
       <c r="G12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -933,40 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>119</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>356</v>
+      </c>
+      <c r="G13" t="n">
+        <v>68.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>359</v>
+        <v>767</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>345</v>
+        <v>140</v>
       </c>
       <c r="G15" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>753</v>
+        <v>704</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>266</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>702</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>253</v>
+        <v>981</v>
       </c>
       <c r="G19" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>440</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>972</v>
+        <v>252</v>
       </c>
       <c r="G21" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1364,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>242</v>
+        <v>365</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>353</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,118 +1468,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>460</v>
       </c>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024.04.13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>广州·潮娃展WWS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>西环路1号 广州岭南会展中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>32</v>
-      </c>
-      <c r="G27" t="n">
-        <v>48</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>454</v>
-      </c>
-      <c r="G28" t="n">
-        <v>69</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
@@ -1751,7 +1669,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1792,7 +1710,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1833,7 +1751,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1874,7 +1792,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2040,7 +1958,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2081,7 +1999,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2122,7 +2040,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
         <v>280</v>
@@ -2222,7 +2140,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2249,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2322,7 +2240,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2344,38 +2262,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>广州·cooperative kingdom同人展2.0</t>
+          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号 岭南电商园</t>
+          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
+          <t>2024.02.23 20:30-02.24 02:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1324</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79264</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lZQgvkwg1701411941873.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2303,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·明日方舟×桌游only茶会</t>
+          <t>广州·ADSL本土动漫创作作品展2024</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>江泰路36号(江泰路地铁站A口步行150米) 中海江泰里</t>
+          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81424</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9tXvlAPU1706516533044.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2344,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·《时间命运：次元使们的开幕礼》 电子音乐现场演出</t>
+          <t>广州·LoveLive!!only聚会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头 MaoLivehouse（太古仓店）</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.23 20:30-02.24 02:30</t>
+          <t>2024.02.24 11:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="G5" t="n">
-        <v>120</v>
+        <v>48.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81752</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/CJGVtPuW1707103176474.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
         </is>
       </c>
     </row>
@@ -2472,33 +2390,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·ADSL本土动漫创作作品展2024</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>芳村大道下市直街1号信义会馆21栋(近白鹅潭风情酒吧街) 信义会馆-21栋</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IdWKAPpg1706783537298.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2513,33 +2431,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·LoveLive!!only聚会</t>
+          <t>广州·国乙Only&amp;代号鸢</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G7" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/PR2aoUkc1706156040096.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -2554,33 +2472,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>389</v>
+        <v>126</v>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2595,33 +2513,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>175</v>
+        <v>1058</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>61.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2636,33 +2554,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>351</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,33 +2595,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1007</v>
+        <v>179</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -2718,33 +2636,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,38 +2672,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -2795,38 +2713,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -2841,33 +2759,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
-      </c>
-      <c r="G15" t="n">
-        <v>35</v>
+        <v>119</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -2877,38 +2797,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>353</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>288</v>
+        <v>118</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -2918,40 +2838,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>119</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>364</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -2961,38 +2879,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3002,38 +2920,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -3043,38 +2961,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>356</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>68.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3089,33 +3007,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>277</v>
+        <v>767</v>
       </c>
       <c r="G21" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3130,33 +3048,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>345</v>
+        <v>140</v>
       </c>
       <c r="G22" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3084,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>753</v>
+        <v>704</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3207,38 +3125,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>135</v>
+        <v>266</v>
       </c>
       <c r="G24" t="n">
-        <v>58</v>
+        <v>68.8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3248,38 +3166,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>702</v>
+        <v>68</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3289,38 +3207,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>253</v>
+        <v>981</v>
       </c>
       <c r="G26" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,33 +3253,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>64</v>
+        <v>440</v>
       </c>
       <c r="G27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3289,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>972</v>
+        <v>84</v>
       </c>
       <c r="G28" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3330,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>东风中路299号 广州中山纪念堂</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>433</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3371,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 19:00-03.17 20:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="G30" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80870</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8WBT7H6W1705376580145.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3412,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>广州·梁祝 ·黄河经典名曲大型管弦交响音乐会</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>东风中路299号 广州中山纪念堂</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81788</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/54YX2MVU1707208994883.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3458,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3554,19 +3472,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>242</v>
+        <v>365</v>
       </c>
       <c r="G32" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,33 +3499,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.23 20:00-03.23 22:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>77</v>
-      </c>
-      <c r="G33" t="n">
-        <v>68</v>
+        <v>626</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3537,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.31 19:00-03.31 20:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>353</v>
+        <v>146</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3658,40 +3578,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>广州·春卷饭 十周年  2024  专场演出</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 20:00-03.23 22:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>626</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>58</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81186</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -3701,38 +3619,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.31</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>广州·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.31 19:00-03.31 20:30</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="G36" t="n">
-        <v>380</v>
+        <v>48</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81422</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -3742,38 +3660,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3783,38 +3701,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>32</v>
+        <v>460</v>
       </c>
       <c r="G38" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3824,118 +3742,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.19</t>
+          <t>2024.04.28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G39" t="n">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>454</v>
-      </c>
-      <c r="G40" t="n">
-        <v>69</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024.04.28</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>中山纪念堂 中山纪念堂</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.04.28 19:30-04.28 21:30</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>11</v>
-      </c>
-      <c r="G41" t="n">
-        <v>280</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G34" t="n">
         <v>380</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G38" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1085</v>
+        <v>1135</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>987</v>
+        <v>1003</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
         <v>58</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1514,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2021,36 +2021,79 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2024.04.24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>广州·今泉爱夏  巡演</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024.04.24 20:00-04.24 21:30</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81890</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/YJENeaUi1708313389899.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>2024.04.28</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>13</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" t="n">
         <v>280</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2140,7 +2183,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2167,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,7 +2283,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2322,7 +2365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2363,7 +2406,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2404,7 +2447,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2445,7 +2488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2527,7 +2570,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1085</v>
+        <v>1135</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2568,7 +2611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2609,7 +2652,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2691,7 +2734,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2732,7 +2775,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2816,7 +2859,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2857,7 +2900,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2939,7 +2982,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G19" t="n">
         <v>380</v>
@@ -2980,7 +3023,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3021,7 +3064,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3062,7 +3105,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3103,7 +3146,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3144,7 +3187,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3185,7 +3228,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3226,7 +3269,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>987</v>
+        <v>1003</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3267,7 +3310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3390,7 +3433,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3431,7 +3474,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3472,7 +3515,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3513,7 +3556,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3556,7 +3599,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G34" t="n">
         <v>380</v>
@@ -3597,7 +3640,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G35" t="n">
         <v>58</v>
@@ -3638,7 +3681,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -3679,7 +3722,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
         <v>64</v>
@@ -3720,7 +3763,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="G38" t="n">
         <v>69</v>
@@ -3742,36 +3785,79 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2024.04.24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>广州·今泉爱夏  巡演</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.04.24 20:00-04.24 21:30</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81890</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/YJENeaUi1708313389899.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>2024.04.28</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F40" t="n">
         <v>13</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G40" t="n">
         <v>280</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1135</v>
+        <v>1156</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
         <v>58</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1135</v>
+        <v>1156</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G19" t="n">
         <v>380</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G35" t="n">
         <v>58</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G38" t="n">
         <v>69</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,10 +665,12 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
-      </c>
-      <c r="G6" t="n">
-        <v>55</v>
+        <v>135</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1156</v>
+        <v>1191</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -747,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -913,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -995,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1068,7 +1070,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1077,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1241,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1282,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1323,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1364,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1446,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -1487,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1587,7 +1589,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>120</v>
@@ -1628,7 +1630,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>420</v>
@@ -1669,7 +1671,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1710,7 +1712,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1751,7 +1753,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1792,7 +1794,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1915,7 +1917,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1958,7 +1960,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2040,12 +2042,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>288</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
         <v>280</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>120</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2529,10 +2529,12 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>132</v>
-      </c>
-      <c r="G8" t="n">
-        <v>55</v>
+        <v>135</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2570,7 +2572,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1156</v>
+        <v>1191</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2611,7 +2613,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2652,7 +2654,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2693,7 +2695,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>420</v>
@@ -2734,7 +2736,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2775,7 +2777,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2859,7 +2861,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2900,7 +2902,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2941,7 +2943,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -2982,7 +2984,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G19" t="n">
         <v>380</v>
@@ -3023,7 +3025,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3064,7 +3066,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3105,7 +3107,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3137,7 +3139,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3146,7 +3148,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3187,7 +3189,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3228,7 +3230,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3269,7 +3271,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3310,7 +3312,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3433,7 +3435,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3474,7 +3476,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3515,7 +3517,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3556,7 +3558,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3599,7 +3601,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G34" t="n">
         <v>380</v>
@@ -3681,7 +3683,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -3763,7 +3765,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="G38" t="n">
         <v>69</v>
@@ -3804,12 +3806,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>288</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
         <v>280</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1191</v>
+        <v>1214</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>288</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1191</v>
+        <v>1214</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G19" t="n">
         <v>380</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G38" t="n">
         <v>69</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>288</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1214</v>
+        <v>1245</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1502,6 +1502,47 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024.05.18</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>广州·恋与深空only</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>大石街石北工业大道644号 巨大创意产业园</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.18 17:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81962</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/a7aqaXrK1708485268977.jpeg</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,7 +1712,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1712,7 +1753,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1753,7 +1794,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
@@ -1794,7 +1835,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1917,7 +1958,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1960,7 +2001,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -1982,38 +2023,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.19</t>
+          <t>2024.04.14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·铃木木乃美 2024 演唱会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.14 19:00-04.14 20:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81911</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rGjpHpAV1708328728461.jpeg</t>
         </is>
       </c>
     </row>
@@ -2023,38 +2064,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.24</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·今泉爱夏  巡演</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.24 20:00-04.24 21:30</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>288</v>
+        <v>64</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/YJENeaUi1708313389899.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -2064,36 +2105,77 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>2024.04.24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>广州·今泉爱夏  巡演</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2024.04.24 20:00-04.24 21:30</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>288</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81890</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/YJENeaUi1708313389899.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>2024.04.28</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>14</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" t="n">
         <v>280</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
         </is>
@@ -2183,7 +2265,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2210,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,7 +2365,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2365,7 +2447,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2406,7 +2488,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2447,7 +2529,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2488,7 +2570,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2572,7 +2654,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1214</v>
+        <v>1245</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2613,7 +2695,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2654,7 +2736,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2736,7 +2818,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2777,7 +2859,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2861,7 +2943,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2902,7 +2984,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2943,7 +3025,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -2984,7 +3066,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G19" t="n">
         <v>380</v>
@@ -3025,7 +3107,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3066,7 +3148,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3107,7 +3189,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3148,7 +3230,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3189,7 +3271,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3230,7 +3312,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3271,7 +3353,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3312,7 +3394,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3435,7 +3517,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3476,7 +3558,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3517,7 +3599,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3558,7 +3640,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3601,7 +3683,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G34" t="n">
         <v>380</v>
@@ -3705,38 +3787,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.19</t>
+          <t>2024.04.14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
+          <t>广州·铃木木乃美 2024 演唱会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>奥体南路12号优托邦购物中心 疆进酒Omni Space GZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.19 19:30-04.19 21:00</t>
+          <t>2024.04.14 19:00-04.14 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="G37" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81911</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rGjpHpAV1708328728461.jpeg</t>
         </is>
       </c>
     </row>
@@ -3746,38 +3828,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·动漫钢琴鬼才Kyle Xian互动演奏会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.19 19:30-04.19 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>478</v>
+        <v>34</v>
       </c>
       <c r="G38" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81434</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DJpXVLjd1706236823839.png</t>
         </is>
       </c>
     </row>
@@ -3787,38 +3869,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.24</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广州·今泉爱夏  巡演</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.24 20:00-04.24 21:30</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>487</v>
       </c>
       <c r="G39" t="n">
-        <v>288</v>
+        <v>69</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/YJENeaUi1708313389899.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -3828,38 +3910,120 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2024.04.24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>广州·今泉爱夏  巡演</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>革新路124号太古仓码头54汇5号仓 太空间Livehouse</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.24 20:00-04.24 21:30</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>288</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81890</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/YJENeaUi1708313389899.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2024.04.28</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve"> 广州·夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>中山纪念堂 中山纪念堂</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2024.04.28 19:30-04.28 21:30</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>14</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>280</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81068</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/pXznRv8G1705633441713.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024.05.18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>广州·恋与深空only</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>大石街石北工业大道644号 巨大创意产业园</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.18 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>22</v>
+      </c>
+      <c r="G42" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81962</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/a7aqaXrK1708485268977.jpeg</t>
         </is>
       </c>
     </row>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G5" t="n">
         <v>63</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1245</v>
+        <v>1261</v>
       </c>
       <c r="G7" t="n">
         <v>61.2</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G13" t="n">
         <v>68.8</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G17" t="n">
         <v>68.8</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="G19" t="n">
         <v>39</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G26" t="n">
         <v>69</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
         <v>64</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G7" t="n">
         <v>63</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1245</v>
+        <v>1261</v>
       </c>
       <c r="G9" t="n">
         <v>61.2</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
         <v>118</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G20" t="n">
         <v>68.8</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G22" t="n">
         <v>58</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G24" t="n">
         <v>68.8</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="G26" t="n">
         <v>39</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G28" t="n">
         <v>380</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G34" t="n">
         <v>380</v>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
         <v>64</v>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G39" t="n">
         <v>69</v>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>

--- a/广州-漫展信息.xlsx
+++ b/广州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G2" t="n">
         <v>49</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G3" t="n">
         <v>48.8</v>
@@ -569,33 +569,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·国乙Only&amp;代号鸢（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>454</v>
-      </c>
-      <c r="G4" t="n">
-        <v>48</v>
+        <v>215</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +612,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>216</v>
-      </c>
-      <c r="G5" t="n">
-        <v>63</v>
+        <v>136</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,35 +655,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>136</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1301</v>
+      </c>
+      <c r="G6" t="n">
+        <v>68</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1261</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>61.2</v>
+        <v>35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -730,38 +732,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>425</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
+        <v>120</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -771,38 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>389</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +816,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>444</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>68.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -853,40 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>814</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +898,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>389</v>
+        <v>205</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>437</v>
+        <v>746</v>
       </c>
       <c r="G13" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>809</v>
+        <v>310</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 13:00-03.17 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>195</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>741</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>304</v>
+        <v>1049</v>
       </c>
       <c r="G17" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -1147,33 +1149,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>492</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·BanG Dream ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1045</v>
+        <v>287</v>
       </c>
       <c r="G19" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,38 +1226,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·原神X星穹铁道X绝区零ONLY</t>
+          <t>广州·排球少年ONLY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>486</v>
+        <v>407</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,38 +1267,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·BanG Dream ONLY</t>
+          <t>广州·妖都恋与制作人ONLY3.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>迎宾大道123号 赛仑吉地大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>286</v>
+        <v>101</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/3HJiKSeD1707104926306.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1308,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·妖都恋与制作人ONLY3.0</t>
+          <t>广州·运动番only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>迎宾大道123号 赛仑吉地大酒店</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="G22" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81715</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/RVh3xReW1707031240390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1349,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·排球少年ONLY</t>
+          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.13 10:00-04.13 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>397</v>
+        <v>29</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80716</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IFLvYmxx1704879325152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1395,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·Veni Vidi Vici动漫游戏嘉年华</t>
+          <t>广州·潮娃展WWS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>西环路1号 广州岭南会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1407,19 +1409,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G24" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7ir7DZHt1706697841803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,38 +1431,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·潮娃展WWS</t>
+          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>西环路1号 广州岭南会展中心</t>
+          <t>同泰路颐和山庄 颐和大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.13 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>50</v>
+        <v>489</v>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81745</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/1SWNaBsA1707100228293.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
         </is>
       </c>
     </row>
@@ -1470,38 +1472,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·Arknights Only·夜航星（明日方舟Only)</t>
+          <t>广州·第八届萌物语动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>同泰路颐和山庄 颐和大酒店</t>
+          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>488</v>
+        <v>433</v>
       </c>
       <c r="G26" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80282</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gaEHIE1F1703745559785.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1712,7 +1714,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G4" t="n">
         <v>288</v>
@@ -1753,7 +1755,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>118</v>
@@ -1835,7 +1837,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -1876,7 +1878,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -1917,7 +1919,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2001,7 +2003,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2042,7 +2044,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2083,7 +2085,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
         <v>64</v>
@@ -2124,7 +2126,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>288</v>
@@ -2165,7 +2167,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
         <v>280</v>
@@ -2265,7 +2267,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2365,7 +2367,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2447,7 +2449,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -2488,7 +2490,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G5" t="n">
         <v>48.8</v>
@@ -2515,33 +2517,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广州·SISP动漫游戏嘉年华</t>
+          <t>广州·国乙Only&amp;代号鸢（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>西湾路150号 悦汇城</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>454</v>
-      </c>
-      <c r="G6" t="n">
-        <v>48</v>
+        <v>215</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
         </is>
       </c>
     </row>
@@ -2556,33 +2560,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广州·国乙Only&amp;代号鸢</t>
+          <t>广州·无限动漫展 国潮限定版</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 21:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>216</v>
-      </c>
-      <c r="G7" t="n">
-        <v>63</v>
+        <v>136</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81763</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q58IwJyS1707118330731.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
         </is>
       </c>
     </row>
@@ -2597,35 +2603,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州·无限动漫展 国潮限定版</t>
+          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>芳村花地大道309号(花地湾地铁站A口步行390米) 花地湾生活馆</t>
+          <t>东沙大道16号 广州国际医药港</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>136</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1301</v>
+      </c>
+      <c r="G8" t="n">
+        <v>68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/kl74TuHi1706255717866.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2640,33 +2644,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>广州·砂糖桔动漫荟STJ01·综合同人展</t>
+          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东沙大道16号 广州国际医药港</t>
+          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 20:00-02.24 22:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1261</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>61.2</v>
+        <v>420</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80774</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/DVyct79W1705032375001.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
         </is>
       </c>
     </row>
@@ -2676,38 +2680,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>广州·第八届萌物语动漫嘉年华</t>
+          <t>广州·2024幻毛纪聚会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>洛浦街厦滘西环路1号 岭南会展中心</t>
+          <t>体育西路54号 星之光潮领地</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>425</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/c4bBhKzu1706685824726.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
         </is>
       </c>
     </row>
@@ -2717,38 +2721,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州·运动番only</t>
+          <t>广州·「十年之约」封茗囧菌2024个唱</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.25 15:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>207</v>
+        <v>376</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/TBZfwnB41706255329549.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
         </is>
       </c>
     </row>
@@ -2758,38 +2762,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州黄龄【有没有吃过饭】LIVEHOUSE巡演—广州站</t>
+          <t>广州·第五届清云动漫展（取消）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>新港东路磨碟沙大街118号第8栋 媒棚LIVE</t>
+          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 20:00-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
-      </c>
-      <c r="G12" t="n">
-        <v>420</v>
+        <v>120</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80205</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/W0RuZh771703573375987.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
         </is>
       </c>
     </row>
@@ -2799,38 +2805,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州·2024幻毛纪聚会</t>
+          <t>广州·COS STAR次元之夜ACG主题派对</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育西路54号 星之光潮领地</t>
+          <t>南洲路158号2F SD Livehouse</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 18:00</t>
+          <t>2024.03.02 19:00-03.02 22:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/bQ7AY7LY1706690509681.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
         </is>
       </c>
     </row>
@@ -2840,38 +2846,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>广州·「十年之约」封茗囧菌2024个唱</t>
+          <t>广州·明日方舟ONLY</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>恩宁路265号三层四层自编01 MAO Livehouse广州（永庆坊店）</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 15:00-02.25 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="G14" t="n">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81462</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/GADzCRlp1706260895679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
         </is>
       </c>
     </row>
@@ -2881,40 +2887,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>广州·第五届清云动漫展（取消）</t>
+          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>丰乐北路898号 雅居乐黄埔创新中心</t>
+          <t>人民北路696号 广州友谊剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 10:30-03.03 15:10</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>120</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="G15" t="n">
+        <v>78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80502</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8twXfPtk1704436405178.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
         </is>
       </c>
     </row>
@@ -2924,38 +2928,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>广州·COS STAR次元之夜ACG主题派对</t>
+          <t>广州·HANAPOKO 2024 LIVE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南洲路158号2F SD Livehouse</t>
+          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 19:00-03.02 22:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>291</v>
       </c>
       <c r="G16" t="n">
-        <v>118</v>
+        <v>380</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81755</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/7PANdxoY1707105412800.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
         </is>
       </c>
     </row>
@@ -2965,38 +2969,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>广州·明日方舟ONLY</t>
+          <t>广州·VOCALOID术力口only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 09:30-03.09 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80271</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/O9z5j7RB1703733578857.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
         </is>
       </c>
     </row>
@@ -3006,38 +3010,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>广州·《奥特传奇之希望之光》圆谷正版授权奥特曼系列舞台剧</t>
+          <t>广州·排球少年.only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>人民北路696号 广州友谊剧院</t>
+          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.03 10:30-03.03 15:10</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>814</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81023</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/r6OKUMAF1705997977504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3052,33 +3056,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州·HANAPOKO 2024 LIVE</t>
+          <t>广州·樱漫动漫嘉年华9.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>海珠同创汇东一街11号（上冲南约11-2） 声音共和Livehouse</t>
+          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>290</v>
+        <v>205</v>
       </c>
       <c r="G19" t="n">
-        <v>380</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81279</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tMZ1Jp2G1705992352054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
         </is>
       </c>
     </row>
@@ -3088,38 +3092,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州·VOCALOID术力口only</t>
+          <t>广州·进击的巨人only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 09:30-03.09 18:00</t>
+          <t>2024.03.10 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>437</v>
+        <v>746</v>
       </c>
       <c r="G20" t="n">
-        <v>68.8</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/XpsHJTsC1706160000879.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3133,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州·排球少年.only</t>
+          <t>广州·马娘only2024</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>广龙路中油BP(白云万顺达南加油站)北侧约260米 李宁运动中心</t>
+          <t>黄边三横路一街1号 设计殿堂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.10 09:30-03.10 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>809</v>
+        <v>310</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80453</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JYZdnQHl1704341212206.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
         </is>
       </c>
     </row>
@@ -3170,38 +3174,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广州·樱漫动漫嘉年华9.0</t>
+          <t>广州·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>奥体南路12号 优托邦(奥体旗舰店)</t>
+          <t>西湾路150号 悦汇城</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 13:00-03.17 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>195</v>
+        <v>462</v>
       </c>
       <c r="G22" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80624</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gBrd7lLX1707203945413.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Z4Q6Fv8B1704770554777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3211,38 +3215,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州·进击的巨人only</t>
+          <t>广州·YU 7th动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>机场路1399号广州百信广场二期 李宁运动中心</t>
+          <t>珠江西路8号 高德置地夏广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.10 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>741</v>
+        <v>91</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80454</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/m8QkMfFl1704347300282.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
         </is>
       </c>
     </row>
@@ -3252,38 +3256,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.10</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州·马娘only2024</t>
+          <t>广州·代号鸢only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>黄边三横路一街1号 设计殿堂</t>
+          <t>清河东路288号 科尔海悦酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.10 09:30-03.10 18:00</t>
+          <t>2024.03.16 10:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>304</v>
+        <v>1049</v>
       </c>
       <c r="G24" t="n">
-        <v>68.8</v>
+        <v>39</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81632</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79828</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/svWCXpKm1706776489024.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/RVUVc8oy1702549585918.jpeg</t>
         </is>
       </c>
     </row>
@@ -3298,33 +3302,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>广州·YU 7th动漫嘉年华</t>
+          <t>广州·原神X星穹铁道X绝区零ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>珠江西路8号 高德置地夏广场</t>
+          <t>洛浦街夏滘西环路1号(厦滘地铁站A口步行290米) 厦喾岭南电商园会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>87</v>
+        <v>492</v>
       </c>
       <c r="G25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80715</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/lVqoZMVQ1706775042937.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Lt6ZYvA41704878219924.jpeg</t>
         </is>
       </c>
     </row>
@@ -3334,38 +3338,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广州·代号鸢only2.0</t>
+          <t>广州·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>清河东路288号 科尔海悦酒店</t>
+          <t>恩宁路265号三层、四层自编01 MAO Livehouse广州(永庆坊店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 21:00</t>
+          <t>2024.03.17 19:00-03.17 20:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1045</v>
+        <v>88</v>
       </c>
       <c r="G26" t="n">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detai